--- a/data/final_predictions/xlsx/pred_Study_4_reviews.xlsx
+++ b/data/final_predictions/xlsx/pred_Study_4_reviews.xlsx
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="R2" t="n">
-        <v>-0.51</v>
+        <v>-0.89</v>
       </c>
       <c r="S2" t="n">
         <v>3.5</v>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="R3" t="n">
-        <v>-0.5</v>
+        <v>0.25</v>
       </c>
       <c r="S3" t="n">
         <v>7</v>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="R4" t="n">
-        <v>-0.51</v>
+        <v>0.53</v>
       </c>
       <c r="S4" t="n">
         <v>3.5</v>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="R5" t="n">
-        <v>-0.48</v>
+        <v>0.09</v>
       </c>
       <c r="S5" t="n">
         <v>6.5</v>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="R6" t="n">
-        <v>-0.49</v>
+        <v>0.13</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -826,7 +826,7 @@
         </is>
       </c>
       <c r="R7" t="n">
-        <v>-0.51</v>
+        <v>-0.88</v>
       </c>
       <c r="S7" t="n">
         <v>1.5</v>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="R8" t="n">
-        <v>-0.5</v>
+        <v>0.77</v>
       </c>
       <c r="S8" t="n">
         <v>4</v>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>-0.52</v>
+        <v>-0.01</v>
       </c>
       <c r="S9" t="n">
         <v>4</v>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="R10" t="n">
-        <v>-0.5</v>
+        <v>0.13</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1040,7 +1040,7 @@
         </is>
       </c>
       <c r="R11" t="n">
-        <v>-0.49</v>
+        <v>0.18</v>
       </c>
       <c r="S11" t="n">
         <v>4</v>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="R12" t="n">
-        <v>-0.51</v>
+        <v>-0.43</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1142,7 +1142,7 @@
         </is>
       </c>
       <c r="R13" t="n">
-        <v>-0.48</v>
+        <v>0.91</v>
       </c>
       <c r="S13" t="n">
         <v>8</v>
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="R14" t="n">
-        <v>-0.49</v>
+        <v>0.13</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="R15" t="n">
-        <v>-0.53</v>
+        <v>-0.95</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="R16" t="n">
-        <v>-0.5</v>
+        <v>-0.88</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="R17" t="n">
-        <v>-0.51</v>
+        <v>-0.4</v>
       </c>
       <c r="S17" t="n">
         <v>2</v>
@@ -1403,7 +1403,7 @@
         </is>
       </c>
       <c r="R18" t="n">
-        <v>-0.5</v>
+        <v>0.44</v>
       </c>
       <c r="S18" t="n">
         <v>7</v>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="R19" t="n">
-        <v>-0.5</v>
+        <v>-0.41</v>
       </c>
       <c r="S19" t="n">
         <v>4</v>
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="R20" t="n">
-        <v>-0.51</v>
+        <v>-0.96</v>
       </c>
       <c r="S20" t="n">
         <v>1.5</v>
@@ -1564,7 +1564,7 @@
         </is>
       </c>
       <c r="R21" t="n">
-        <v>-0.5</v>
+        <v>0.31</v>
       </c>
       <c r="S21" t="n">
         <v>6</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="R22" t="n">
-        <v>-0.49</v>
+        <v>-0.41</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="R23" t="n">
-        <v>-0.49</v>
+        <v>0.22</v>
       </c>
       <c r="S23" t="n">
         <v>6.5</v>
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>-0.49</v>
+        <v>0.98</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="R25" t="n">
-        <v>-0.51</v>
+        <v>-0.76</v>
       </c>
       <c r="S25" t="n">
         <v>1.5</v>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="R26" t="n">
-        <v>-0.51</v>
+        <v>-0.92</v>
       </c>
       <c r="S26" t="n">
         <v>2</v>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="R27" t="n">
-        <v>-0.49</v>
+        <v>0.8</v>
       </c>
       <c r="S27" t="n">
         <v>7</v>
@@ -1933,7 +1933,7 @@
         </is>
       </c>
       <c r="R28" t="n">
-        <v>-0.49</v>
+        <v>-0.64</v>
       </c>
       <c r="S28" t="n">
         <v>4.5</v>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="R29" t="n">
-        <v>-0.52</v>
+        <v>-0.9</v>
       </c>
       <c r="S29" t="n">
         <v>2</v>
@@ -2041,7 +2041,7 @@
         </is>
       </c>
       <c r="R30" t="n">
-        <v>-0.49</v>
+        <v>-0.21</v>
       </c>
       <c r="S30" t="n">
         <v>3.5</v>
@@ -2092,7 +2092,7 @@
         </is>
       </c>
       <c r="R31" t="n">
-        <v>-0.51</v>
+        <v>-0.4</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="R32" t="n">
-        <v>-0.49</v>
+        <v>0.06</v>
       </c>
       <c r="S32" t="n">
         <v>4.5</v>
@@ -2196,7 +2196,7 @@
         </is>
       </c>
       <c r="R33" t="n">
-        <v>-0.49</v>
+        <v>-0.95</v>
       </c>
       <c r="S33" t="n">
         <v>2</v>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="R34" t="n">
-        <v>-0.49</v>
+        <v>0.13</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="R35" t="n">
-        <v>-0.49</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="S35" t="n">
         <v>6</v>
@@ -2353,7 +2353,7 @@
         </is>
       </c>
       <c r="R36" t="n">
-        <v>-0.49</v>
+        <v>-0.45</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -2404,7 +2404,7 @@
         </is>
       </c>
       <c r="R37" t="n">
-        <v>-0.49</v>
+        <v>0.13</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -2457,7 +2457,7 @@
         </is>
       </c>
       <c r="R38" t="n">
-        <v>-0.5</v>
+        <v>-0.83</v>
       </c>
       <c r="S38" t="n">
         <v>1.5</v>
@@ -2508,7 +2508,7 @@
         </is>
       </c>
       <c r="R39" t="n">
-        <v>-0.5</v>
+        <v>0.55</v>
       </c>
       <c r="S39" t="n">
         <v>7.5</v>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="R40" t="n">
-        <v>-0.49</v>
+        <v>-0.87</v>
       </c>
       <c r="S40" t="n">
         <v>2.5</v>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="R41" t="n">
-        <v>-0.51</v>
+        <v>0.87</v>
       </c>
       <c r="S41" t="n">
         <v>7</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="R42" t="n">
-        <v>-0.51</v>
+        <v>0.71</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="R43" t="n">
-        <v>-0.48</v>
+        <v>-0.97</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="R44" t="n">
-        <v>-0.5</v>
+        <v>-0.96</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -2816,7 +2816,7 @@
         </is>
       </c>
       <c r="R45" t="n">
-        <v>-0.48</v>
+        <v>0.87</v>
       </c>
       <c r="S45" t="n">
         <v>7.5</v>
@@ -2867,7 +2867,7 @@
         </is>
       </c>
       <c r="R46" t="n">
-        <v>-0.5</v>
+        <v>-0.14</v>
       </c>
       <c r="S46" t="n">
         <v>2.5</v>
@@ -2918,7 +2918,7 @@
         </is>
       </c>
       <c r="R47" t="n">
-        <v>-0.49</v>
+        <v>0.8</v>
       </c>
       <c r="S47" t="n">
         <v>7</v>
@@ -2973,7 +2973,7 @@
         </is>
       </c>
       <c r="R48" t="n">
-        <v>-0.51</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="S48" t="n">
         <v>0.5</v>
@@ -3024,7 +3024,7 @@
         </is>
       </c>
       <c r="R49" t="n">
-        <v>-0.48</v>
+        <v>0.67</v>
       </c>
       <c r="S49" t="n">
         <v>8.5</v>
@@ -3075,7 +3075,7 @@
         </is>
       </c>
       <c r="R50" t="n">
-        <v>-0.49</v>
+        <v>0.13</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="R51" t="n">
-        <v>-0.5</v>
+        <v>0.32</v>
       </c>
       <c r="S51" t="n">
         <v>7</v>
@@ -3177,7 +3177,7 @@
         </is>
       </c>
       <c r="R52" t="n">
-        <v>-0.51</v>
+        <v>-0.4</v>
       </c>
       <c r="S52" t="n">
         <v>2</v>
@@ -3230,7 +3230,7 @@
         </is>
       </c>
       <c r="R53" t="n">
-        <v>-0.49</v>
+        <v>0.91</v>
       </c>
       <c r="S53" t="n">
         <v>8</v>
@@ -3283,7 +3283,7 @@
         </is>
       </c>
       <c r="R54" t="n">
-        <v>-0.49</v>
+        <v>0.98</v>
       </c>
       <c r="S54" t="n">
         <v>8.5</v>
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="R55" t="n">
-        <v>-0.5</v>
+        <v>0.55</v>
       </c>
       <c r="S55" t="n">
         <v>7.5</v>
@@ -3387,7 +3387,7 @@
         </is>
       </c>
       <c r="R56" t="n">
-        <v>-0.51</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="S56" t="n">
         <v>2.5</v>
@@ -3489,7 +3489,7 @@
         </is>
       </c>
       <c r="R58" t="n">
-        <v>-0.48</v>
+        <v>0.09</v>
       </c>
       <c r="S58" t="n">
         <v>6.5</v>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="R59" t="n">
-        <v>-0.5</v>
+        <v>-0.05</v>
       </c>
       <c r="S59" t="n">
         <v>3</v>
@@ -3595,7 +3595,7 @@
         </is>
       </c>
       <c r="R60" t="n">
-        <v>-0.5</v>
+        <v>-0.85</v>
       </c>
       <c r="S60" t="n">
         <v>2.5</v>
@@ -3648,7 +3648,7 @@
         </is>
       </c>
       <c r="R61" t="n">
-        <v>-0.5</v>
+        <v>-0.27</v>
       </c>
       <c r="S61" t="n">
         <v>2</v>
@@ -3699,7 +3699,7 @@
         </is>
       </c>
       <c r="R62" t="n">
-        <v>-0.5</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="S62" t="n">
         <v>2.5</v>
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="R63" t="n">
-        <v>-0.48</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S63" t="n">
         <v>8.5</v>
@@ -3805,7 +3805,7 @@
         </is>
       </c>
       <c r="R64" t="n">
-        <v>-0.5</v>
+        <v>0.25</v>
       </c>
       <c r="S64" t="n">
         <v>7</v>
@@ -3858,7 +3858,7 @@
         </is>
       </c>
       <c r="R65" t="n">
-        <v>-0.5</v>
+        <v>0.09</v>
       </c>
       <c r="S65" t="n">
         <v>6</v>
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="R66" t="n">
-        <v>-0.5</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="S66" t="n">
         <v>3.5</v>
@@ -3962,7 +3962,7 @@
         </is>
       </c>
       <c r="R67" t="n">
-        <v>-0.51</v>
+        <v>-0.39</v>
       </c>
       <c r="S67" t="n">
         <v>3.5</v>
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="R68" t="n">
-        <v>-0.52</v>
+        <v>0.47</v>
       </c>
       <c r="S68" t="n">
         <v>4</v>
@@ -4066,7 +4066,7 @@
         </is>
       </c>
       <c r="R69" t="n">
-        <v>-0.49</v>
+        <v>0.13</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="R70" t="n">
-        <v>-0.48</v>
+        <v>0.88</v>
       </c>
       <c r="S70" t="n">
         <v>8</v>
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="R71" t="n">
-        <v>-0.49</v>
+        <v>0.86</v>
       </c>
       <c r="S71" t="n">
         <v>7.5</v>
@@ -4227,7 +4227,7 @@
         </is>
       </c>
       <c r="R72" t="n">
-        <v>-0.51</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="S72" t="n">
         <v>2.5</v>
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="R73" t="n">
-        <v>-0.51</v>
+        <v>-0.4</v>
       </c>
       <c r="S73" t="n">
         <v>2</v>
@@ -4329,7 +4329,7 @@
         </is>
       </c>
       <c r="R74" t="n">
-        <v>-0.49</v>
+        <v>-0.01</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -4380,7 +4380,7 @@
         </is>
       </c>
       <c r="R75" t="n">
-        <v>-0.48</v>
+        <v>0.22</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -4433,7 +4433,7 @@
         </is>
       </c>
       <c r="R76" t="n">
-        <v>-0.5</v>
+        <v>0.96</v>
       </c>
       <c r="S76" t="n">
         <v>7</v>
@@ -4484,7 +4484,7 @@
         </is>
       </c>
       <c r="R77" t="n">
-        <v>-0.48</v>
+        <v>0.09</v>
       </c>
       <c r="S77" t="n">
         <v>6.5</v>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="R78" t="n">
-        <v>-0.5</v>
+        <v>0.2</v>
       </c>
       <c r="S78" t="n">
         <v>4</v>
@@ -4592,7 +4592,7 @@
         </is>
       </c>
       <c r="R79" t="n">
-        <v>-0.5</v>
+        <v>0.04</v>
       </c>
       <c r="S79" t="n">
         <v>7</v>
@@ -4643,7 +4643,7 @@
         </is>
       </c>
       <c r="R80" t="n">
-        <v>-0.49</v>
+        <v>-0.87</v>
       </c>
       <c r="S80" t="n">
         <v>2.5</v>
@@ -4694,7 +4694,7 @@
         </is>
       </c>
       <c r="R81" t="n">
-        <v>-0.49</v>
+        <v>-0.13</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="R82" t="n">
-        <v>-0.5</v>
+        <v>-0.86</v>
       </c>
       <c r="S82" t="n">
         <v>3</v>
@@ -4798,7 +4798,7 @@
         </is>
       </c>
       <c r="R83" t="n">
-        <v>-0.5</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="S83" t="n">
         <v>7.5</v>
@@ -4849,7 +4849,7 @@
         </is>
       </c>
       <c r="R84" t="n">
-        <v>-0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="S84" t="n">
         <v>3.5</v>
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="R85" t="n">
-        <v>-0.48</v>
+        <v>0.09</v>
       </c>
       <c r="S85" t="n">
         <v>6.5</v>
@@ -4953,7 +4953,7 @@
         </is>
       </c>
       <c r="R86" t="n">
-        <v>-0.51</v>
+        <v>-0.13</v>
       </c>
       <c r="S86" t="n">
         <v>4</v>
@@ -5006,7 +5006,7 @@
         </is>
       </c>
       <c r="R87" t="n">
-        <v>-0.51</v>
+        <v>-0.83</v>
       </c>
       <c r="S87" t="n">
         <v>2</v>
@@ -5059,7 +5059,7 @@
         </is>
       </c>
       <c r="R88" t="n">
-        <v>-0.49</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S88" t="n">
         <v>8</v>
@@ -5114,7 +5114,7 @@
         </is>
       </c>
       <c r="R89" t="n">
-        <v>-0.49</v>
+        <v>0.86</v>
       </c>
       <c r="S89" t="n">
         <v>7.5</v>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="R90" t="n">
-        <v>-0.49</v>
+        <v>0.97</v>
       </c>
       <c r="S90" t="n">
         <v>7</v>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="R91" t="n">
-        <v>-0.51</v>
+        <v>0.12</v>
       </c>
       <c r="S91" t="n">
         <v>7</v>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="R92" t="n">
-        <v>-0.51</v>
+        <v>-0.43</v>
       </c>
       <c r="S92" t="n">
         <v>2</v>
@@ -5326,7 +5326,7 @@
         </is>
       </c>
       <c r="R93" t="n">
-        <v>-0.51</v>
+        <v>-0.4</v>
       </c>
       <c r="S93" t="n">
         <v>2</v>
@@ -5379,7 +5379,7 @@
         </is>
       </c>
       <c r="R94" t="n">
-        <v>-0.5</v>
+        <v>0.13</v>
       </c>
       <c r="S94" t="n">
         <v>3</v>
@@ -5485,7 +5485,7 @@
         </is>
       </c>
       <c r="R96" t="n">
-        <v>-0.51</v>
+        <v>0.87</v>
       </c>
       <c r="S96" t="n">
         <v>7</v>
@@ -5536,7 +5536,7 @@
         </is>
       </c>
       <c r="R97" t="n">
-        <v>-0.48</v>
+        <v>0.4</v>
       </c>
       <c r="S97" t="n">
         <v>6</v>
@@ -5587,7 +5587,7 @@
         </is>
       </c>
       <c r="R98" t="n">
-        <v>-0.51</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c r="R99" t="n">
-        <v>-0.51</v>
+        <v>0.65</v>
       </c>
       <c r="S99" t="n">
         <v>6.5</v>
@@ -5697,7 +5697,7 @@
         </is>
       </c>
       <c r="R100" t="n">
-        <v>-0.49</v>
+        <v>0.63</v>
       </c>
       <c r="S100" t="n">
         <v>5</v>
@@ -5752,7 +5752,7 @@
         </is>
       </c>
       <c r="R101" t="n">
-        <v>-0.5</v>
+        <v>-0.31</v>
       </c>
       <c r="S101" t="n">
         <v>4</v>
@@ -5807,7 +5807,7 @@
         </is>
       </c>
       <c r="R102" t="n">
-        <v>-0.49</v>
+        <v>-0.39</v>
       </c>
       <c r="S102" t="n">
         <v>3</v>
@@ -5860,7 +5860,7 @@
         </is>
       </c>
       <c r="R103" t="n">
-        <v>-0.5</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="S103" t="n">
         <v>2.5</v>
@@ -5915,7 +5915,7 @@
         </is>
       </c>
       <c r="R104" t="n">
-        <v>-0.5</v>
+        <v>-0.53</v>
       </c>
       <c r="S104" t="n">
         <v>2</v>
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="R105" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="S105" t="n">
         <v>3</v>
@@ -6021,7 +6021,7 @@
         </is>
       </c>
       <c r="R106" t="n">
-        <v>-0.51</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="S106" t="n">
         <v>1</v>
@@ -6074,7 +6074,7 @@
         </is>
       </c>
       <c r="R107" t="n">
-        <v>-0.5</v>
+        <v>-0.89</v>
       </c>
       <c r="S107" t="n">
         <v>1</v>
@@ -6125,7 +6125,7 @@
         </is>
       </c>
       <c r="R108" t="n">
-        <v>-0.51</v>
+        <v>-0.91</v>
       </c>
       <c r="S108" t="n">
         <v>1.5</v>
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="R109" t="n">
-        <v>-0.51</v>
+        <v>-0.82</v>
       </c>
       <c r="S109" t="n">
         <v>2</v>
@@ -6235,7 +6235,7 @@
         </is>
       </c>
       <c r="R110" t="n">
-        <v>-0.51</v>
+        <v>-0.38</v>
       </c>
       <c r="S110" t="n">
         <v>2.5</v>
@@ -6286,7 +6286,7 @@
         </is>
       </c>
       <c r="R111" t="n">
-        <v>-0.5</v>
+        <v>-0.88</v>
       </c>
       <c r="S111" t="n">
         <v>1</v>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="R112" t="n">
-        <v>-0.52</v>
+        <v>-0.23</v>
       </c>
       <c r="S112" t="n">
         <v>2.5</v>
@@ -6392,7 +6392,7 @@
         </is>
       </c>
       <c r="R113" t="n">
-        <v>-0.52</v>
+        <v>-0.73</v>
       </c>
       <c r="S113" t="n">
         <v>2.5</v>
@@ -6443,7 +6443,7 @@
         </is>
       </c>
       <c r="R114" t="n">
-        <v>-0.49</v>
+        <v>-0.76</v>
       </c>
       <c r="S114" t="n">
         <v>1.5</v>
@@ -6494,7 +6494,7 @@
         </is>
       </c>
       <c r="R115" t="n">
-        <v>-0.49</v>
+        <v>-0.88</v>
       </c>
       <c r="S115" t="n">
         <v>1.5</v>
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="R116" t="n">
-        <v>-0.5</v>
+        <v>-0.91</v>
       </c>
       <c r="S116" t="n">
         <v>0.5</v>
@@ -6596,7 +6596,7 @@
         </is>
       </c>
       <c r="R117" t="n">
-        <v>-0.49</v>
+        <v>-0.82</v>
       </c>
       <c r="S117" t="n">
         <v>1.5</v>
@@ -6647,7 +6647,7 @@
         </is>
       </c>
       <c r="R118" t="n">
-        <v>-0.49</v>
+        <v>-0.96</v>
       </c>
       <c r="S118" t="n">
         <v>2</v>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="R119" t="n">
-        <v>-0.5</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="S119" t="n">
         <v>2</v>
@@ -6751,7 +6751,7 @@
         </is>
       </c>
       <c r="R120" t="n">
-        <v>-0.5</v>
+        <v>-0.78</v>
       </c>
       <c r="S120" t="n">
         <v>2</v>
@@ -6802,7 +6802,7 @@
         </is>
       </c>
       <c r="R121" t="n">
-        <v>-0.49</v>
+        <v>0.13</v>
       </c>
       <c r="S121" t="n">
         <v>5</v>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="R122" t="n">
-        <v>-0.5</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="S122" t="n">
         <v>4</v>
@@ -6910,7 +6910,7 @@
         </is>
       </c>
       <c r="R123" t="n">
-        <v>-0.5</v>
+        <v>-0.92</v>
       </c>
       <c r="S123" t="n">
         <v>2</v>
@@ -6961,7 +6961,7 @@
         </is>
       </c>
       <c r="R124" t="n">
-        <v>-0.49</v>
+        <v>-0.92</v>
       </c>
       <c r="S124" t="n">
         <v>1</v>
@@ -7012,7 +7012,7 @@
         </is>
       </c>
       <c r="R125" t="n">
-        <v>-0.51</v>
+        <v>-0.4</v>
       </c>
       <c r="S125" t="n">
         <v>2</v>
@@ -7063,7 +7063,7 @@
         </is>
       </c>
       <c r="R126" t="n">
-        <v>-0.48</v>
+        <v>0.09</v>
       </c>
       <c r="S126" t="n">
         <v>6.5</v>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="R127" t="n">
-        <v>-0.5</v>
+        <v>-0.95</v>
       </c>
       <c r="S127" t="n">
         <v>2.5</v>
@@ -7169,7 +7169,7 @@
         </is>
       </c>
       <c r="R128" t="n">
-        <v>-0.48</v>
+        <v>-0.87</v>
       </c>
       <c r="S128" t="n">
         <v>2.5</v>
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="R129" t="n">
-        <v>-0.5</v>
+        <v>-0.97</v>
       </c>
       <c r="S129" t="n">
         <v>1.5</v>
@@ -7273,7 +7273,7 @@
         </is>
       </c>
       <c r="R130" t="n">
-        <v>-0.5</v>
+        <v>-0.23</v>
       </c>
       <c r="S130" t="n">
         <v>2</v>
@@ -7324,7 +7324,7 @@
         </is>
       </c>
       <c r="R131" t="n">
-        <v>-0.5</v>
+        <v>-0.88</v>
       </c>
       <c r="S131" t="n">
         <v>1</v>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="R132" t="n">
-        <v>-0.49</v>
+        <v>0.13</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -7432,7 +7432,7 @@
         </is>
       </c>
       <c r="R133" t="n">
-        <v>-0.51</v>
+        <v>-0.96</v>
       </c>
       <c r="S133" t="n">
         <v>1.5</v>
@@ -7485,7 +7485,7 @@
         </is>
       </c>
       <c r="R134" t="n">
-        <v>-0.52</v>
+        <v>-0.95</v>
       </c>
       <c r="S134" t="n">
         <v>2</v>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="R135" t="n">
-        <v>-0.5</v>
+        <v>-0.18</v>
       </c>
       <c r="S135" t="n">
         <v>2.5</v>
@@ -7591,7 +7591,7 @@
         </is>
       </c>
       <c r="R136" t="n">
-        <v>-0.5</v>
+        <v>-0.89</v>
       </c>
       <c r="S136" t="n">
         <v>1</v>
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="R137" t="n">
-        <v>-0.5</v>
+        <v>-0.88</v>
       </c>
       <c r="S137" t="n">
         <v>1</v>
@@ -7695,7 +7695,7 @@
         </is>
       </c>
       <c r="R138" t="n">
-        <v>-0.5</v>
+        <v>-0.93</v>
       </c>
       <c r="S138" t="n">
         <v>1.5</v>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="R139" t="n">
-        <v>-0.5</v>
+        <v>-0.49</v>
       </c>
       <c r="S139" t="n">
         <v>2</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="R140" t="n">
-        <v>-0.49</v>
+        <v>-0.95</v>
       </c>
       <c r="S140" t="n">
         <v>3</v>
@@ -7848,7 +7848,7 @@
         </is>
       </c>
       <c r="R141" t="n">
-        <v>-0.49</v>
+        <v>-0.92</v>
       </c>
       <c r="S141" t="n">
         <v>1</v>
@@ -7901,7 +7901,7 @@
         </is>
       </c>
       <c r="R142" t="n">
-        <v>-0.51</v>
+        <v>-0.2</v>
       </c>
       <c r="S142" t="n">
         <v>2.5</v>
@@ -7954,7 +7954,7 @@
         </is>
       </c>
       <c r="R143" t="n">
-        <v>-0.51</v>
+        <v>-0.28</v>
       </c>
       <c r="S143" t="n">
         <v>2</v>
@@ -8009,7 +8009,7 @@
         </is>
       </c>
       <c r="R144" t="n">
-        <v>-0.49</v>
+        <v>-0.01</v>
       </c>
       <c r="S144" t="n">
         <v>3.5</v>
@@ -8060,7 +8060,7 @@
         </is>
       </c>
       <c r="R145" t="n">
-        <v>-0.51</v>
+        <v>-0.4</v>
       </c>
       <c r="S145" t="n">
         <v>2</v>
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="R146" t="n">
-        <v>-0.49</v>
+        <v>-0.92</v>
       </c>
       <c r="S146" t="n">
         <v>1</v>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="R147" t="n">
-        <v>-0.51</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="S147" t="n">
         <v>2.5</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="R148" t="n">
-        <v>-0.5</v>
+        <v>-0.88</v>
       </c>
       <c r="S148" t="n">
         <v>1</v>
@@ -8264,7 +8264,7 @@
         </is>
       </c>
       <c r="R149" t="n">
-        <v>-0.49</v>
+        <v>-0.95</v>
       </c>
       <c r="S149" t="n">
         <v>1</v>
@@ -8321,7 +8321,7 @@
         </is>
       </c>
       <c r="R150" t="n">
-        <v>-0.49</v>
+        <v>-0.97</v>
       </c>
       <c r="S150" t="n">
         <v>1</v>
@@ -8374,7 +8374,7 @@
         </is>
       </c>
       <c r="R151" t="n">
-        <v>-0.5</v>
+        <v>-0.89</v>
       </c>
       <c r="S151" t="n">
         <v>1</v>
@@ -8425,7 +8425,7 @@
         </is>
       </c>
       <c r="R152" t="n">
-        <v>-0.49</v>
+        <v>-0.88</v>
       </c>
       <c r="S152" t="n">
         <v>1.5</v>
@@ -8476,7 +8476,7 @@
         </is>
       </c>
       <c r="R153" t="n">
-        <v>-0.5</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="S153" t="n">
         <v>2.5</v>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="R154" t="n">
-        <v>-0.51</v>
+        <v>-0.57</v>
       </c>
       <c r="S154" t="n">
         <v>1.5</v>
@@ -8580,7 +8580,7 @@
         </is>
       </c>
       <c r="R155" t="n">
-        <v>-0.5</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="S155" t="n">
         <v>1.5</v>
@@ -8637,7 +8637,7 @@
         </is>
       </c>
       <c r="R156" t="n">
-        <v>-0.51</v>
+        <v>0.8</v>
       </c>
       <c r="S156" t="n">
         <v>7</v>
@@ -8692,7 +8692,7 @@
         </is>
       </c>
       <c r="R157" t="n">
-        <v>-0.49</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="S157" t="n">
         <v>3</v>
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="R158" t="n">
-        <v>-0.51</v>
+        <v>-0.22</v>
       </c>
       <c r="S158" t="n">
         <v>2</v>
@@ -8798,7 +8798,7 @@
         </is>
       </c>
       <c r="R159" t="n">
-        <v>-0.51</v>
+        <v>-0.9</v>
       </c>
       <c r="S159" t="n">
         <v>1.5</v>
@@ -8849,7 +8849,7 @@
         </is>
       </c>
       <c r="R160" t="n">
-        <v>-0.49</v>
+        <v>-0.95</v>
       </c>
       <c r="S160" t="n">
         <v>2</v>
@@ -8900,7 +8900,7 @@
         </is>
       </c>
       <c r="R161" t="n">
-        <v>-0.5</v>
+        <v>-0.51</v>
       </c>
       <c r="S161" t="n">
         <v>1.5</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="R162" t="n">
-        <v>-0.51</v>
+        <v>-0.96</v>
       </c>
       <c r="S162" t="n">
         <v>3</v>
@@ -9004,7 +9004,7 @@
         </is>
       </c>
       <c r="R163" t="n">
-        <v>-0.49</v>
+        <v>-0.02</v>
       </c>
       <c r="S163" t="n">
         <v>3</v>
@@ -9059,7 +9059,7 @@
         </is>
       </c>
       <c r="R164" t="n">
-        <v>-0.51</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="S164" t="n">
         <v>2</v>
@@ -9110,7 +9110,7 @@
         </is>
       </c>
       <c r="R165" t="n">
-        <v>-0.51</v>
+        <v>-0.43</v>
       </c>
       <c r="S165" t="n">
         <v>2</v>
@@ -9163,7 +9163,7 @@
         </is>
       </c>
       <c r="R166" t="n">
-        <v>-0.5</v>
+        <v>-0.97</v>
       </c>
       <c r="S166" t="n">
         <v>0.5</v>
@@ -9214,7 +9214,7 @@
         </is>
       </c>
       <c r="R167" t="n">
-        <v>-0.49</v>
+        <v>-0.72</v>
       </c>
       <c r="S167" t="n">
         <v>1.5</v>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="R168" t="n">
-        <v>-0.51</v>
+        <v>0.25</v>
       </c>
       <c r="S168" t="n">
         <v>2</v>
@@ -9318,7 +9318,7 @@
         </is>
       </c>
       <c r="R169" t="n">
-        <v>-0.5</v>
+        <v>-0.92</v>
       </c>
       <c r="S169" t="n">
         <v>2.5</v>
@@ -9369,7 +9369,7 @@
         </is>
       </c>
       <c r="R170" t="n">
-        <v>-0.49</v>
+        <v>0.13</v>
       </c>
       <c r="S170" t="n">
         <v>5</v>
@@ -9422,7 +9422,7 @@
         </is>
       </c>
       <c r="R171" t="n">
-        <v>-0.48</v>
+        <v>-0.97</v>
       </c>
       <c r="S171" t="n">
         <v>1.5</v>
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="R172" t="n">
-        <v>-0.49</v>
+        <v>-0.41</v>
       </c>
       <c r="S172" t="n">
         <v>3</v>
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="R173" t="n">
-        <v>-0.51</v>
+        <v>-0.96</v>
       </c>
       <c r="S173" t="n">
         <v>3</v>
@@ -9577,7 +9577,7 @@
         </is>
       </c>
       <c r="R174" t="n">
-        <v>-0.5</v>
+        <v>-0.26</v>
       </c>
       <c r="S174" t="n">
         <v>2</v>
@@ -9628,7 +9628,7 @@
         </is>
       </c>
       <c r="R175" t="n">
-        <v>-0.5</v>
+        <v>-0.88</v>
       </c>
       <c r="S175" t="n">
         <v>1</v>
@@ -9679,7 +9679,7 @@
         </is>
       </c>
       <c r="R176" t="n">
-        <v>-0.48</v>
+        <v>0.06</v>
       </c>
       <c r="S176" t="n">
         <v>6</v>
@@ -9730,7 +9730,7 @@
         </is>
       </c>
       <c r="R177" t="n">
-        <v>-0.49</v>
+        <v>-0.31</v>
       </c>
       <c r="S177" t="n">
         <v>2.5</v>
@@ -9781,7 +9781,7 @@
         </is>
       </c>
       <c r="R178" t="n">
-        <v>-0.51</v>
+        <v>-0.4</v>
       </c>
       <c r="S178" t="n">
         <v>2</v>
@@ -9832,7 +9832,7 @@
         </is>
       </c>
       <c r="R179" t="n">
-        <v>-0.49</v>
+        <v>-0.92</v>
       </c>
       <c r="S179" t="n">
         <v>1</v>
@@ -9887,7 +9887,7 @@
         </is>
       </c>
       <c r="R180" t="n">
-        <v>-0.52</v>
+        <v>-0.73</v>
       </c>
       <c r="S180" t="n">
         <v>2.5</v>
@@ -9942,7 +9942,7 @@
         </is>
       </c>
       <c r="R181" t="n">
-        <v>-0.5</v>
+        <v>-0.96</v>
       </c>
       <c r="S181" t="n">
         <v>2</v>
@@ -9995,7 +9995,7 @@
         </is>
       </c>
       <c r="R182" t="n">
-        <v>-0.5</v>
+        <v>-0.9</v>
       </c>
       <c r="S182" t="n">
         <v>1.5</v>
@@ -10046,7 +10046,7 @@
         </is>
       </c>
       <c r="R183" t="n">
-        <v>-0.5</v>
+        <v>-0.88</v>
       </c>
       <c r="S183" t="n">
         <v>1</v>
@@ -10097,7 +10097,7 @@
         </is>
       </c>
       <c r="R184" t="n">
-        <v>-0.48</v>
+        <v>-0.95</v>
       </c>
       <c r="S184" t="n">
         <v>2</v>
@@ -10150,7 +10150,7 @@
         </is>
       </c>
       <c r="R185" t="n">
-        <v>-0.51</v>
+        <v>-0.29</v>
       </c>
       <c r="S185" t="n">
         <v>2.5</v>
@@ -10201,7 +10201,7 @@
         </is>
       </c>
       <c r="R186" t="n">
-        <v>-0.5</v>
+        <v>-0.88</v>
       </c>
       <c r="S186" t="n">
         <v>1</v>
@@ -10256,7 +10256,7 @@
         </is>
       </c>
       <c r="R187" t="n">
-        <v>-0.5</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="S187" t="n">
         <v>2.5</v>
@@ -10311,7 +10311,7 @@
         </is>
       </c>
       <c r="R188" t="n">
-        <v>-0.51</v>
+        <v>-0.97</v>
       </c>
       <c r="S188" t="n">
         <v>2</v>
@@ -10364,7 +10364,7 @@
         </is>
       </c>
       <c r="R189" t="n">
-        <v>-0.5</v>
+        <v>-0.96</v>
       </c>
       <c r="S189" t="n">
         <v>1</v>
@@ -10415,7 +10415,7 @@
         </is>
       </c>
       <c r="R190" t="n">
-        <v>-0.49</v>
+        <v>-0.74</v>
       </c>
       <c r="S190" t="n">
         <v>2</v>
@@ -10468,7 +10468,7 @@
         </is>
       </c>
       <c r="R191" t="n">
-        <v>-0.48</v>
+        <v>-0.97</v>
       </c>
       <c r="S191" t="n">
         <v>3.5</v>
@@ -10525,7 +10525,7 @@
         </is>
       </c>
       <c r="R192" t="n">
-        <v>-0.51</v>
+        <v>-0.97</v>
       </c>
       <c r="S192" t="n">
         <v>1</v>
@@ -10578,7 +10578,7 @@
         </is>
       </c>
       <c r="R193" t="n">
-        <v>-0.5</v>
+        <v>-0.76</v>
       </c>
       <c r="S193" t="n">
         <v>5.5</v>
@@ -10633,7 +10633,7 @@
         </is>
       </c>
       <c r="R194" t="n">
-        <v>-0.51</v>
+        <v>-0.98</v>
       </c>
       <c r="S194" t="n">
         <v>2.5</v>
@@ -10684,7 +10684,7 @@
         </is>
       </c>
       <c r="R195" t="n">
-        <v>-0.51</v>
+        <v>-0.4</v>
       </c>
       <c r="S195" t="n">
         <v>2</v>
@@ -10739,7 +10739,7 @@
         </is>
       </c>
       <c r="R196" t="n">
-        <v>-0.48</v>
+        <v>-0.87</v>
       </c>
       <c r="S196" t="n">
         <v>2.5</v>
@@ -10790,7 +10790,7 @@
         </is>
       </c>
       <c r="R197" t="n">
-        <v>-0.5</v>
+        <v>-0.88</v>
       </c>
       <c r="S197" t="n">
         <v>1</v>
@@ -10841,7 +10841,7 @@
         </is>
       </c>
       <c r="R198" t="n">
-        <v>-0.49</v>
+        <v>-0.88</v>
       </c>
       <c r="S198" t="n">
         <v>1.5</v>
@@ -10892,7 +10892,7 @@
         </is>
       </c>
       <c r="R199" t="n">
-        <v>-0.51</v>
+        <v>-0.96</v>
       </c>
       <c r="S199" t="n">
         <v>2</v>
@@ -10947,7 +10947,7 @@
         </is>
       </c>
       <c r="R200" t="n">
-        <v>-0.51</v>
+        <v>-0.76</v>
       </c>
       <c r="S200" t="n">
         <v>1.5</v>
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="R201" t="n">
-        <v>-0.5</v>
+        <v>-0.97</v>
       </c>
       <c r="S201" t="n">
         <v>2</v>
@@ -11053,7 +11053,7 @@
         </is>
       </c>
       <c r="R202" t="n">
-        <v>-0.51</v>
+        <v>-0.95</v>
       </c>
       <c r="S202" t="n">
         <v>3</v>
@@ -11106,7 +11106,7 @@
         </is>
       </c>
       <c r="R203" t="n">
-        <v>-0.5</v>
+        <v>-0.76</v>
       </c>
       <c r="S203" t="n">
         <v>1.5</v>
@@ -11157,7 +11157,7 @@
         </is>
       </c>
       <c r="R204" t="n">
-        <v>-0.5</v>
+        <v>-0.26</v>
       </c>
       <c r="S204" t="n">
         <v>2</v>
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="R205" t="n">
-        <v>-0.51</v>
+        <v>-0.7</v>
       </c>
       <c r="S205" t="n">
         <v>2.5</v>
@@ -11261,7 +11261,7 @@
         </is>
       </c>
       <c r="R206" t="n">
-        <v>-0.49</v>
+        <v>-0.92</v>
       </c>
       <c r="S206" t="n">
         <v>1</v>
@@ -11316,7 +11316,7 @@
         </is>
       </c>
       <c r="R207" t="n">
-        <v>-0.48</v>
+        <v>-0.83</v>
       </c>
       <c r="S207" t="n">
         <v>2.5</v>
@@ -11371,7 +11371,7 @@
         </is>
       </c>
       <c r="R208" t="n">
-        <v>-0.5</v>
+        <v>-0.16</v>
       </c>
       <c r="S208" t="n">
         <v>3.5</v>
@@ -11422,7 +11422,7 @@
         </is>
       </c>
       <c r="R209" t="n">
-        <v>-0.51</v>
+        <v>-0.75</v>
       </c>
       <c r="S209" t="n">
         <v>2</v>
@@ -11473,7 +11473,7 @@
         </is>
       </c>
       <c r="R210" t="n">
-        <v>-0.49</v>
+        <v>-0.85</v>
       </c>
       <c r="S210" t="n">
         <v>1</v>
@@ -11524,7 +11524,7 @@
         </is>
       </c>
       <c r="R211" t="n">
-        <v>-0.5</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="S211" t="n">
         <v>0.5</v>
@@ -11577,7 +11577,7 @@
         </is>
       </c>
       <c r="R212" t="n">
-        <v>-0.49</v>
+        <v>-0.96</v>
       </c>
       <c r="S212" t="n">
         <v>2</v>
@@ -11632,7 +11632,7 @@
         </is>
       </c>
       <c r="R213" t="n">
-        <v>-0.5</v>
+        <v>-0.88</v>
       </c>
       <c r="S213" t="n">
         <v>1.5</v>
@@ -11687,7 +11687,7 @@
         </is>
       </c>
       <c r="R214" t="n">
-        <v>-0.51</v>
+        <v>-0.95</v>
       </c>
       <c r="S214" t="n">
         <v>1</v>
@@ -11740,7 +11740,7 @@
         </is>
       </c>
       <c r="R215" t="n">
-        <v>-0.5</v>
+        <v>-0.42</v>
       </c>
       <c r="S215" t="n">
         <v>3.5</v>
@@ -11791,7 +11791,7 @@
         </is>
       </c>
       <c r="R216" t="n">
-        <v>-0.5</v>
+        <v>-0.88</v>
       </c>
       <c r="S216" t="n">
         <v>1</v>
@@ -11842,7 +11842,7 @@
         </is>
       </c>
       <c r="R217" t="n">
-        <v>-0.49</v>
+        <v>-0.92</v>
       </c>
       <c r="S217" t="n">
         <v>1</v>
@@ -11893,7 +11893,7 @@
         </is>
       </c>
       <c r="R218" t="n">
-        <v>-0.51</v>
+        <v>-0.4</v>
       </c>
       <c r="S218" t="n">
         <v>2</v>
@@ -11946,7 +11946,7 @@
         </is>
       </c>
       <c r="R219" t="n">
-        <v>-0.49</v>
+        <v>-0.92</v>
       </c>
       <c r="S219" t="n">
         <v>2</v>
@@ -12001,7 +12001,7 @@
         </is>
       </c>
       <c r="R220" t="n">
-        <v>-0.49</v>
+        <v>-0.93</v>
       </c>
       <c r="S220" t="n">
         <v>2.5</v>
@@ -12052,7 +12052,7 @@
         </is>
       </c>
       <c r="R221" t="n">
-        <v>-0.49</v>
+        <v>-0.82</v>
       </c>
       <c r="S221" t="n">
         <v>2.5</v>
@@ -12103,7 +12103,7 @@
         </is>
       </c>
       <c r="R222" t="n">
-        <v>-0.5</v>
+        <v>-0.72</v>
       </c>
       <c r="S222" t="n">
         <v>4</v>
@@ -12154,7 +12154,7 @@
         </is>
       </c>
       <c r="R223" t="n">
-        <v>-0.5</v>
+        <v>-0.97</v>
       </c>
       <c r="S223" t="n">
         <v>1</v>
@@ -12207,7 +12207,7 @@
         </is>
       </c>
       <c r="R224" t="n">
-        <v>-0.51</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="S224" t="n">
         <v>1.5</v>
@@ -12258,7 +12258,7 @@
         </is>
       </c>
       <c r="R225" t="n">
-        <v>-0.5</v>
+        <v>-0.91</v>
       </c>
       <c r="S225" t="n">
         <v>0.5</v>
@@ -12309,7 +12309,7 @@
         </is>
       </c>
       <c r="R226" t="n">
-        <v>-0.5</v>
+        <v>-0.19</v>
       </c>
       <c r="S226" t="n">
         <v>3.5</v>
@@ -12360,7 +12360,7 @@
         </is>
       </c>
       <c r="R227" t="n">
-        <v>-0.48</v>
+        <v>-0.95</v>
       </c>
       <c r="S227" t="n">
         <v>1.5</v>
@@ -12415,7 +12415,7 @@
         </is>
       </c>
       <c r="R228" t="n">
-        <v>-0.51</v>
+        <v>-0.52</v>
       </c>
       <c r="S228" t="n">
         <v>2.5</v>
@@ -12466,7 +12466,7 @@
         </is>
       </c>
       <c r="R229" t="n">
-        <v>-0.49</v>
+        <v>-0.92</v>
       </c>
       <c r="S229" t="n">
         <v>1</v>
@@ -12521,7 +12521,7 @@
         </is>
       </c>
       <c r="R230" t="n">
-        <v>-0.52</v>
+        <v>-0.85</v>
       </c>
       <c r="S230" t="n">
         <v>2</v>
@@ -12572,7 +12572,7 @@
         </is>
       </c>
       <c r="R231" t="n">
-        <v>-0.5</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="S231" t="n">
         <v>2</v>
@@ -12623,7 +12623,7 @@
         </is>
       </c>
       <c r="R232" t="n">
-        <v>-0.49</v>
+        <v>-0.97</v>
       </c>
       <c r="S232" t="n">
         <v>1</v>
@@ -12674,7 +12674,7 @@
         </is>
       </c>
       <c r="R233" t="n">
-        <v>-0.49</v>
+        <v>0.13</v>
       </c>
       <c r="S233" t="n">
         <v>5</v>
@@ -12725,7 +12725,7 @@
         </is>
       </c>
       <c r="R234" t="n">
-        <v>-0.51</v>
+        <v>-0.4</v>
       </c>
       <c r="S234" t="n">
         <v>2</v>
@@ -12780,7 +12780,7 @@
         </is>
       </c>
       <c r="R235" t="n">
-        <v>-0.51</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="S235" t="n">
         <v>1.5</v>
@@ -12833,7 +12833,7 @@
         </is>
       </c>
       <c r="R236" t="n">
-        <v>-0.53</v>
+        <v>-0.97</v>
       </c>
       <c r="S236" t="n">
         <v>1</v>
@@ -12888,7 +12888,7 @@
         </is>
       </c>
       <c r="R237" t="n">
-        <v>-0.52</v>
+        <v>-0.86</v>
       </c>
       <c r="S237" t="n">
         <v>3</v>
@@ -12941,7 +12941,7 @@
         </is>
       </c>
       <c r="R238" t="n">
-        <v>-0.5</v>
+        <v>0.7</v>
       </c>
       <c r="S238" t="n">
         <v>3</v>
@@ -12992,7 +12992,7 @@
         </is>
       </c>
       <c r="R239" t="n">
-        <v>-0.5</v>
+        <v>-0.88</v>
       </c>
       <c r="S239" t="n">
         <v>1</v>
@@ -13043,7 +13043,7 @@
         </is>
       </c>
       <c r="R240" t="n">
-        <v>-0.5</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="S240" t="n">
         <v>2</v>
@@ -13096,7 +13096,7 @@
         </is>
       </c>
       <c r="R241" t="n">
-        <v>-0.5</v>
+        <v>-0.89</v>
       </c>
       <c r="S241" t="n">
         <v>1</v>
@@ -13147,7 +13147,7 @@
         </is>
       </c>
       <c r="R242" t="n">
-        <v>-0.51</v>
+        <v>-0.75</v>
       </c>
       <c r="S242" t="n">
         <v>3.5</v>
@@ -13198,7 +13198,7 @@
         </is>
       </c>
       <c r="R243" t="n">
-        <v>-0.49</v>
+        <v>-0.91</v>
       </c>
       <c r="S243" t="n">
         <v>0.5</v>
@@ -13249,7 +13249,7 @@
         </is>
       </c>
       <c r="R244" t="n">
-        <v>-0.5</v>
+        <v>-0.91</v>
       </c>
       <c r="S244" t="n">
         <v>1.5</v>
@@ -13300,7 +13300,7 @@
         </is>
       </c>
       <c r="R245" t="n">
-        <v>-0.5</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="S245" t="n">
         <v>2</v>
@@ -13357,7 +13357,7 @@
         </is>
       </c>
       <c r="R246" t="n">
-        <v>-0.5</v>
+        <v>-0.98</v>
       </c>
       <c r="S246" t="n">
         <v>1</v>
@@ -13414,7 +13414,7 @@
         </is>
       </c>
       <c r="R247" t="n">
-        <v>-0.49</v>
+        <v>-0.96</v>
       </c>
       <c r="S247" t="n">
         <v>1</v>
@@ -13471,7 +13471,7 @@
         </is>
       </c>
       <c r="R248" t="n">
-        <v>-0.5</v>
+        <v>-0.96</v>
       </c>
       <c r="S248" t="n">
         <v>1.5</v>
@@ -13524,7 +13524,7 @@
         </is>
       </c>
       <c r="R249" t="n">
-        <v>-0.51</v>
+        <v>-0.17</v>
       </c>
       <c r="S249" t="n">
         <v>3.5</v>
@@ -13575,7 +13575,7 @@
         </is>
       </c>
       <c r="R250" t="n">
-        <v>-0.5</v>
+        <v>-0.88</v>
       </c>
       <c r="S250" t="n">
         <v>1</v>
@@ -13626,7 +13626,7 @@
         </is>
       </c>
       <c r="R251" t="n">
-        <v>-0.49</v>
+        <v>-0.95</v>
       </c>
       <c r="S251" t="n">
         <v>0.5</v>
@@ -13681,7 +13681,7 @@
         </is>
       </c>
       <c r="R252" t="n">
-        <v>-0.5</v>
+        <v>-0.28</v>
       </c>
       <c r="S252" t="n">
         <v>3</v>
@@ -13736,7 +13736,7 @@
         </is>
       </c>
       <c r="R253" t="n">
-        <v>-0.52</v>
+        <v>-0.31</v>
       </c>
       <c r="S253" t="n">
         <v>2.5</v>
@@ -13789,7 +13789,7 @@
         </is>
       </c>
       <c r="R254" t="n">
-        <v>-0.49</v>
+        <v>-0.88</v>
       </c>
       <c r="S254" t="n">
         <v>1.5</v>
@@ -13840,7 +13840,7 @@
         </is>
       </c>
       <c r="R255" t="n">
-        <v>-0.5</v>
+        <v>-0.88</v>
       </c>
       <c r="S255" t="n">
         <v>1</v>
@@ -13891,7 +13891,7 @@
         </is>
       </c>
       <c r="R256" t="n">
-        <v>-0.49</v>
+        <v>-0.76</v>
       </c>
       <c r="S256" t="n">
         <v>2</v>
@@ -13944,7 +13944,7 @@
         </is>
       </c>
       <c r="R257" t="n">
-        <v>-0.51</v>
+        <v>-0.84</v>
       </c>
       <c r="S257" t="n">
         <v>0.5</v>
@@ -13995,7 +13995,7 @@
         </is>
       </c>
       <c r="R258" t="n">
-        <v>-0.49</v>
+        <v>-0.91</v>
       </c>
       <c r="S258" t="n">
         <v>3</v>
@@ -14048,7 +14048,7 @@
         </is>
       </c>
       <c r="R259" t="n">
-        <v>-0.49</v>
+        <v>-0.5</v>
       </c>
       <c r="S259" t="n">
         <v>2</v>
@@ -14099,7 +14099,7 @@
         </is>
       </c>
       <c r="R260" t="n">
-        <v>-0.51</v>
+        <v>-0.4</v>
       </c>
       <c r="S260" t="n">
         <v>2</v>
@@ -14152,7 +14152,7 @@
         </is>
       </c>
       <c r="R261" t="n">
-        <v>-0.52</v>
+        <v>-0.58</v>
       </c>
       <c r="S261" t="n">
         <v>2.5</v>
@@ -14203,7 +14203,7 @@
         </is>
       </c>
       <c r="R262" t="n">
-        <v>-0.49</v>
+        <v>0.75</v>
       </c>
       <c r="S262" t="n">
         <v>7.5</v>
@@ -14254,7 +14254,7 @@
         </is>
       </c>
       <c r="R263" t="n">
-        <v>-0.49</v>
+        <v>-0.92</v>
       </c>
       <c r="S263" t="n">
         <v>1</v>
@@ -14307,7 +14307,7 @@
         </is>
       </c>
       <c r="R264" t="n">
-        <v>-0.52</v>
+        <v>-0.54</v>
       </c>
       <c r="S264" t="n">
         <v>2</v>
@@ -14358,7 +14358,7 @@
         </is>
       </c>
       <c r="R265" t="n">
-        <v>-0.49</v>
+        <v>-0.88</v>
       </c>
       <c r="S265" t="n">
         <v>1.5</v>
@@ -14409,7 +14409,7 @@
         </is>
       </c>
       <c r="R266" t="n">
-        <v>-0.5</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="S266" t="n">
         <v>2.5</v>
@@ -14464,7 +14464,7 @@
         </is>
       </c>
       <c r="R267" t="n">
-        <v>-0.5</v>
+        <v>0.01</v>
       </c>
       <c r="S267" t="n">
         <v>2.5</v>
@@ -14515,7 +14515,7 @@
         </is>
       </c>
       <c r="R268" t="n">
-        <v>-0.5</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="S268" t="n">
         <v>1.5</v>
@@ -14566,7 +14566,7 @@
         </is>
       </c>
       <c r="R269" t="n">
-        <v>-0.5</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="S269" t="n">
         <v>2</v>
@@ -14619,7 +14619,7 @@
         </is>
       </c>
       <c r="R270" t="n">
-        <v>-0.5</v>
+        <v>-0.96</v>
       </c>
       <c r="S270" t="n">
         <v>1</v>
@@ -14670,7 +14670,7 @@
         </is>
       </c>
       <c r="R271" t="n">
-        <v>-0.49</v>
+        <v>-0.97</v>
       </c>
       <c r="S271" t="n">
         <v>1</v>
@@ -14723,7 +14723,7 @@
         </is>
       </c>
       <c r="R272" t="n">
-        <v>-0.48</v>
+        <v>-0.97</v>
       </c>
       <c r="S272" t="n">
         <v>1.5</v>
@@ -14774,7 +14774,7 @@
         </is>
       </c>
       <c r="R273" t="n">
-        <v>-0.51</v>
+        <v>-0.4</v>
       </c>
       <c r="S273" t="n">
         <v>2</v>
@@ -14827,7 +14827,7 @@
         </is>
       </c>
       <c r="R274" t="n">
-        <v>-0.49</v>
+        <v>0.64</v>
       </c>
       <c r="S274" t="n">
         <v>7.5</v>
@@ -14882,7 +14882,7 @@
         </is>
       </c>
       <c r="R275" t="n">
-        <v>-0.52</v>
+        <v>-0.87</v>
       </c>
       <c r="S275" t="n">
         <v>2.5</v>
@@ -14933,7 +14933,7 @@
         </is>
       </c>
       <c r="R276" t="n">
-        <v>-0.48</v>
+        <v>0.09</v>
       </c>
       <c r="S276" t="n">
         <v>6.5</v>
@@ -14984,7 +14984,7 @@
         </is>
       </c>
       <c r="R277" t="n">
-        <v>-0.49</v>
+        <v>-0.92</v>
       </c>
       <c r="S277" t="n">
         <v>1</v>
@@ -15035,7 +15035,7 @@
         </is>
       </c>
       <c r="R278" t="n">
-        <v>-0.49</v>
+        <v>-0.84</v>
       </c>
       <c r="S278" t="n">
         <v>2.5</v>
@@ -15088,7 +15088,7 @@
         </is>
       </c>
       <c r="R279" t="n">
-        <v>-0.51</v>
+        <v>-0.89</v>
       </c>
       <c r="S279" t="n">
         <v>2.5</v>
@@ -15139,7 +15139,7 @@
         </is>
       </c>
       <c r="R280" t="n">
-        <v>-0.49</v>
+        <v>0.02</v>
       </c>
       <c r="S280" t="n">
         <v>5</v>
@@ -15190,7 +15190,7 @@
         </is>
       </c>
       <c r="R281" t="n">
-        <v>-0.49</v>
+        <v>-0.92</v>
       </c>
       <c r="S281" t="n">
         <v>1</v>
@@ -15241,7 +15241,7 @@
         </is>
       </c>
       <c r="R282" t="n">
-        <v>-0.5</v>
+        <v>-0.88</v>
       </c>
       <c r="S282" t="n">
         <v>1</v>
@@ -15292,7 +15292,7 @@
         </is>
       </c>
       <c r="R283" t="n">
-        <v>-0.49</v>
+        <v>-0.82</v>
       </c>
       <c r="S283" t="n">
         <v>2.5</v>
@@ -15345,7 +15345,7 @@
         </is>
       </c>
       <c r="R284" t="n">
-        <v>-0.51</v>
+        <v>-0.53</v>
       </c>
       <c r="S284" t="n">
         <v>1.5</v>
@@ -15396,7 +15396,7 @@
         </is>
       </c>
       <c r="R285" t="n">
-        <v>-0.5</v>
+        <v>-0.93</v>
       </c>
       <c r="S285" t="n">
         <v>-0</v>
@@ -15447,7 +15447,7 @@
         </is>
       </c>
       <c r="R286" t="n">
-        <v>-0.5</v>
+        <v>-0.92</v>
       </c>
       <c r="S286" t="n">
         <v>1</v>
@@ -15498,7 +15498,7 @@
         </is>
       </c>
       <c r="R287" t="n">
-        <v>-0.5</v>
+        <v>-0.88</v>
       </c>
       <c r="S287" t="n">
         <v>1</v>
@@ -15549,7 +15549,7 @@
         </is>
       </c>
       <c r="R288" t="n">
-        <v>-0.51</v>
+        <v>-0.92</v>
       </c>
       <c r="S288" t="n">
         <v>2</v>
@@ -15602,7 +15602,7 @@
         </is>
       </c>
       <c r="R289" t="n">
-        <v>-0.52</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="S289" t="n">
         <v>2</v>
@@ -15655,7 +15655,7 @@
         </is>
       </c>
       <c r="R290" t="n">
-        <v>-0.5</v>
+        <v>-0.96</v>
       </c>
       <c r="S290" t="n">
         <v>0</v>
@@ -15706,7 +15706,7 @@
         </is>
       </c>
       <c r="R291" t="n">
-        <v>-0.49</v>
+        <v>-0.91</v>
       </c>
       <c r="S291" t="n">
         <v>2</v>
@@ -15759,7 +15759,7 @@
         </is>
       </c>
       <c r="R292" t="n">
-        <v>-0.51</v>
+        <v>-0.91</v>
       </c>
       <c r="S292" t="n">
         <v>2.5</v>
@@ -15810,7 +15810,7 @@
         </is>
       </c>
       <c r="R293" t="n">
-        <v>-0.49</v>
+        <v>-0.96</v>
       </c>
       <c r="S293" t="n">
         <v>2.5</v>
@@ -15863,7 +15863,7 @@
         </is>
       </c>
       <c r="R294" t="n">
-        <v>-0.49</v>
+        <v>-0.89</v>
       </c>
       <c r="S294" t="n">
         <v>0.5</v>
@@ -15914,7 +15914,7 @@
         </is>
       </c>
       <c r="R295" t="n">
-        <v>-0.49</v>
+        <v>-0.92</v>
       </c>
       <c r="S295" t="n">
         <v>2</v>
@@ -15965,7 +15965,7 @@
         </is>
       </c>
       <c r="R296" t="n">
-        <v>-0.49</v>
+        <v>-0.97</v>
       </c>
       <c r="S296" t="n">
         <v>1</v>
@@ -16018,7 +16018,7 @@
         </is>
       </c>
       <c r="R297" t="n">
-        <v>-0.5</v>
+        <v>-0.05</v>
       </c>
       <c r="S297" t="n">
         <v>3</v>
@@ -16069,7 +16069,7 @@
         </is>
       </c>
       <c r="R298" t="n">
-        <v>-0.5</v>
+        <v>-0.87</v>
       </c>
       <c r="S298" t="n">
         <v>2.5</v>
@@ -16120,7 +16120,7 @@
         </is>
       </c>
       <c r="R299" t="n">
-        <v>-0.49</v>
+        <v>-0.88</v>
       </c>
       <c r="S299" t="n">
         <v>1.5</v>
@@ -16173,7 +16173,7 @@
         </is>
       </c>
       <c r="R300" t="n">
-        <v>-0.5</v>
+        <v>-0.89</v>
       </c>
       <c r="S300" t="n">
         <v>1</v>
@@ -16224,7 +16224,7 @@
         </is>
       </c>
       <c r="R301" t="n">
-        <v>-0.5</v>
+        <v>-0.01</v>
       </c>
       <c r="S301" t="n">
         <v>3</v>
@@ -16275,7 +16275,7 @@
         </is>
       </c>
       <c r="R302" t="n">
-        <v>-0.49</v>
+        <v>-0.88</v>
       </c>
       <c r="S302" t="n">
         <v>1.5</v>
@@ -16326,7 +16326,7 @@
         </is>
       </c>
       <c r="R303" t="n">
-        <v>-0.49</v>
+        <v>0.13</v>
       </c>
       <c r="S303" t="n">
         <v>5</v>
@@ -16379,7 +16379,7 @@
         </is>
       </c>
       <c r="R304" t="n">
-        <v>-0.49</v>
+        <v>-0.59</v>
       </c>
       <c r="S304" t="n">
         <v>2.5</v>
@@ -16434,7 +16434,7 @@
         </is>
       </c>
       <c r="R305" t="n">
-        <v>-0.51</v>
+        <v>-0.36</v>
       </c>
       <c r="S305" t="n">
         <v>2</v>
@@ -16491,7 +16491,7 @@
         </is>
       </c>
       <c r="R306" t="n">
-        <v>-0.51</v>
+        <v>-0.96</v>
       </c>
       <c r="S306" t="n">
         <v>1</v>
@@ -16542,7 +16542,7 @@
         </is>
       </c>
       <c r="R307" t="n">
-        <v>-0.51</v>
+        <v>-0.47</v>
       </c>
       <c r="S307" t="n">
         <v>1.5</v>
@@ -16595,7 +16595,7 @@
         </is>
       </c>
       <c r="R308" t="n">
-        <v>-0.51</v>
+        <v>-0.08</v>
       </c>
       <c r="S308" t="n">
         <v>3</v>
@@ -16646,7 +16646,7 @@
         </is>
       </c>
       <c r="R309" t="n">
-        <v>-0.5</v>
+        <v>-0.97</v>
       </c>
       <c r="S309" t="n">
         <v>2</v>
@@ -16697,7 +16697,7 @@
         </is>
       </c>
       <c r="R310" t="n">
-        <v>-0.52</v>
+        <v>-0.91</v>
       </c>
       <c r="S310" t="n">
         <v>1.5</v>
@@ -16748,7 +16748,7 @@
         </is>
       </c>
       <c r="R311" t="n">
-        <v>-0.5</v>
+        <v>-0.89</v>
       </c>
       <c r="S311" t="n">
         <v>2.5</v>
@@ -16799,7 +16799,7 @@
         </is>
       </c>
       <c r="R312" t="n">
-        <v>-0.49</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="S312" t="n">
         <v>3</v>
@@ -16854,7 +16854,7 @@
         </is>
       </c>
       <c r="R313" t="n">
-        <v>-0.5</v>
+        <v>-0.93</v>
       </c>
       <c r="S313" t="n">
         <v>2</v>
@@ -16905,7 +16905,7 @@
         </is>
       </c>
       <c r="R314" t="n">
-        <v>-0.51</v>
+        <v>-0.93</v>
       </c>
       <c r="S314" t="n">
         <v>0.5</v>
@@ -16956,7 +16956,7 @@
         </is>
       </c>
       <c r="R315" t="n">
-        <v>-0.5</v>
+        <v>0.55</v>
       </c>
       <c r="S315" t="n">
         <v>7.5</v>
@@ -17007,7 +17007,7 @@
         </is>
       </c>
       <c r="R316" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="S316" t="n">
         <v>7.5</v>
@@ -17058,7 +17058,7 @@
         </is>
       </c>
       <c r="R317" t="n">
-        <v>-0.48</v>
+        <v>0.97</v>
       </c>
       <c r="S317" t="n">
         <v>8</v>
@@ -17115,7 +17115,7 @@
         </is>
       </c>
       <c r="R318" t="n">
-        <v>-0.5</v>
+        <v>0.62</v>
       </c>
       <c r="S318" t="n">
         <v>6.5</v>
@@ -17166,7 +17166,7 @@
         </is>
       </c>
       <c r="R319" t="n">
-        <v>-0.48</v>
+        <v>0.67</v>
       </c>
       <c r="S319" t="n">
         <v>8.5</v>
@@ -17217,7 +17217,7 @@
         </is>
       </c>
       <c r="R320" t="n">
-        <v>-0.49</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="S320" t="n">
         <v>6</v>
@@ -17270,7 +17270,7 @@
         </is>
       </c>
       <c r="R321" t="n">
-        <v>-0.48</v>
+        <v>0.96</v>
       </c>
       <c r="S321" t="n">
         <v>8.5</v>
@@ -17325,7 +17325,7 @@
         </is>
       </c>
       <c r="R322" t="n">
-        <v>-0.49</v>
+        <v>0.88</v>
       </c>
       <c r="S322" t="n">
         <v>7.5</v>
@@ -17376,7 +17376,7 @@
         </is>
       </c>
       <c r="R323" t="n">
-        <v>-0.48</v>
+        <v>0.84</v>
       </c>
       <c r="S323" t="n">
         <v>7.5</v>
@@ -17427,7 +17427,7 @@
         </is>
       </c>
       <c r="R324" t="n">
-        <v>-0.48</v>
+        <v>0.96</v>
       </c>
       <c r="S324" t="n">
         <v>8</v>
@@ -17478,7 +17478,7 @@
         </is>
       </c>
       <c r="R325" t="n">
-        <v>-0.5</v>
+        <v>0.32</v>
       </c>
       <c r="S325" t="n">
         <v>7</v>
@@ -17529,7 +17529,7 @@
         </is>
       </c>
       <c r="R326" t="n">
-        <v>-0.5</v>
+        <v>0.96</v>
       </c>
       <c r="S326" t="n">
         <v>6.5</v>
@@ -17580,7 +17580,7 @@
         </is>
       </c>
       <c r="R327" t="n">
-        <v>-0.5</v>
+        <v>0.97</v>
       </c>
       <c r="S327" t="n">
         <v>8</v>
@@ -17631,7 +17631,7 @@
         </is>
       </c>
       <c r="R328" t="n">
-        <v>-0.5</v>
+        <v>0.55</v>
       </c>
       <c r="S328" t="n">
         <v>7.5</v>
@@ -17682,7 +17682,7 @@
         </is>
       </c>
       <c r="R329" t="n">
-        <v>-0.49</v>
+        <v>0.8</v>
       </c>
       <c r="S329" t="n">
         <v>7</v>
@@ -17735,7 +17735,7 @@
         </is>
       </c>
       <c r="R330" t="n">
-        <v>-0.49</v>
+        <v>-0.31</v>
       </c>
       <c r="S330" t="n">
         <v>5.5</v>
@@ -17790,7 +17790,7 @@
         </is>
       </c>
       <c r="R331" t="n">
-        <v>-0.51</v>
+        <v>0.83</v>
       </c>
       <c r="S331" t="n">
         <v>7</v>
@@ -17845,7 +17845,7 @@
         </is>
       </c>
       <c r="R332" t="n">
-        <v>-0.5</v>
+        <v>0.98</v>
       </c>
       <c r="S332" t="n">
         <v>8</v>
@@ -17896,7 +17896,7 @@
         </is>
       </c>
       <c r="R333" t="n">
-        <v>-0.49</v>
+        <v>0.18</v>
       </c>
       <c r="S333" t="n">
         <v>9</v>
@@ -17947,7 +17947,7 @@
         </is>
       </c>
       <c r="R334" t="n">
-        <v>-0.49</v>
+        <v>0.13</v>
       </c>
       <c r="S334" t="n">
         <v>5</v>
@@ -18000,7 +18000,7 @@
         </is>
       </c>
       <c r="R335" t="n">
-        <v>-0.51</v>
+        <v>0.96</v>
       </c>
       <c r="S335" t="n">
         <v>7.5</v>
@@ -18051,7 +18051,7 @@
         </is>
       </c>
       <c r="R336" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="S336" t="n">
         <v>7.5</v>
@@ -18102,7 +18102,7 @@
         </is>
       </c>
       <c r="R337" t="n">
-        <v>-0.49</v>
+        <v>0.13</v>
       </c>
       <c r="S337" t="n">
         <v>5</v>
@@ -18153,7 +18153,7 @@
         </is>
       </c>
       <c r="R338" t="n">
-        <v>-0.49</v>
+        <v>0.85</v>
       </c>
       <c r="S338" t="n">
         <v>7.5</v>
@@ -18204,7 +18204,7 @@
         </is>
       </c>
       <c r="R339" t="n">
-        <v>-0.48</v>
+        <v>0.77</v>
       </c>
       <c r="S339" t="n">
         <v>7.5</v>
@@ -18255,7 +18255,7 @@
         </is>
       </c>
       <c r="R340" t="n">
-        <v>-0.49</v>
+        <v>0.18</v>
       </c>
       <c r="S340" t="n">
         <v>9</v>
@@ -18306,7 +18306,7 @@
         </is>
       </c>
       <c r="R341" t="n">
-        <v>-0.49</v>
+        <v>0.8</v>
       </c>
       <c r="S341" t="n">
         <v>7</v>
@@ -18357,7 +18357,7 @@
         </is>
       </c>
       <c r="R342" t="n">
-        <v>-0.5</v>
+        <v>0.73</v>
       </c>
       <c r="S342" t="n">
         <v>8.5</v>
@@ -18408,7 +18408,7 @@
         </is>
       </c>
       <c r="R343" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="S343" t="n">
         <v>7.5</v>
@@ -18459,7 +18459,7 @@
         </is>
       </c>
       <c r="R344" t="n">
-        <v>-0.5</v>
+        <v>0.55</v>
       </c>
       <c r="S344" t="n">
         <v>7.5</v>
@@ -18514,7 +18514,7 @@
         </is>
       </c>
       <c r="R345" t="n">
-        <v>-0.48</v>
+        <v>0.76</v>
       </c>
       <c r="S345" t="n">
         <v>7.5</v>
@@ -18567,7 +18567,7 @@
         </is>
       </c>
       <c r="R346" t="n">
-        <v>-0.48</v>
+        <v>0.44</v>
       </c>
       <c r="S346" t="n">
         <v>7</v>
@@ -18618,7 +18618,7 @@
         </is>
       </c>
       <c r="R347" t="n">
-        <v>-0.5</v>
+        <v>0.55</v>
       </c>
       <c r="S347" t="n">
         <v>7.5</v>
@@ -18673,7 +18673,7 @@
         </is>
       </c>
       <c r="R348" t="n">
-        <v>-0.49</v>
+        <v>0.98</v>
       </c>
       <c r="S348" t="n">
         <v>7.5</v>
@@ -18724,7 +18724,7 @@
         </is>
       </c>
       <c r="R349" t="n">
-        <v>-0.49</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="S349" t="n">
         <v>6</v>
@@ -18777,7 +18777,7 @@
         </is>
       </c>
       <c r="R350" t="n">
-        <v>-0.48</v>
+        <v>0.97</v>
       </c>
       <c r="S350" t="n">
         <v>8.5</v>
@@ -18828,7 +18828,7 @@
         </is>
       </c>
       <c r="R351" t="n">
-        <v>-0.49</v>
+        <v>0.97</v>
       </c>
       <c r="S351" t="n">
         <v>8</v>
@@ -18879,7 +18879,7 @@
         </is>
       </c>
       <c r="R352" t="n">
-        <v>-0.49</v>
+        <v>0.98</v>
       </c>
       <c r="S352" t="n">
         <v>8.5</v>
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="R353" t="n">
-        <v>-0.49</v>
+        <v>0.75</v>
       </c>
       <c r="S353" t="n">
         <v>7.5</v>
@@ -18983,7 +18983,7 @@
         </is>
       </c>
       <c r="R354" t="n">
-        <v>-0.5</v>
+        <v>0.87</v>
       </c>
       <c r="S354" t="n">
         <v>7.5</v>
@@ -19034,7 +19034,7 @@
         </is>
       </c>
       <c r="R355" t="n">
-        <v>-0.5</v>
+        <v>0.55</v>
       </c>
       <c r="S355" t="n">
         <v>7.5</v>
@@ -19085,7 +19085,7 @@
         </is>
       </c>
       <c r="R356" t="n">
-        <v>-0.5</v>
+        <v>0.55</v>
       </c>
       <c r="S356" t="n">
         <v>7.5</v>
@@ -19140,7 +19140,7 @@
         </is>
       </c>
       <c r="R357" t="n">
-        <v>-0.47</v>
+        <v>0.85</v>
       </c>
       <c r="S357" t="n">
         <v>9</v>
@@ -19193,7 +19193,7 @@
         </is>
       </c>
       <c r="R358" t="n">
-        <v>-0.47</v>
+        <v>-0.13</v>
       </c>
       <c r="S358" t="n">
         <v>8.5</v>
@@ -19244,7 +19244,7 @@
         </is>
       </c>
       <c r="R359" t="n">
-        <v>-0.5</v>
+        <v>0.55</v>
       </c>
       <c r="S359" t="n">
         <v>7.5</v>
@@ -19295,7 +19295,7 @@
         </is>
       </c>
       <c r="R360" t="n">
-        <v>-0.48</v>
+        <v>0.67</v>
       </c>
       <c r="S360" t="n">
         <v>8.5</v>
@@ -19346,7 +19346,7 @@
         </is>
       </c>
       <c r="R361" t="n">
-        <v>-0.5</v>
+        <v>0.61</v>
       </c>
       <c r="S361" t="n">
         <v>7.5</v>
@@ -19397,7 +19397,7 @@
         </is>
       </c>
       <c r="R362" t="n">
-        <v>-0.49</v>
+        <v>0.53</v>
       </c>
       <c r="S362" t="n">
         <v>9.5</v>
@@ -19448,7 +19448,7 @@
         </is>
       </c>
       <c r="R363" t="n">
-        <v>-0.5</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S363" t="n">
         <v>7.5</v>
@@ -19499,7 +19499,7 @@
         </is>
       </c>
       <c r="R364" t="n">
-        <v>-0.49</v>
+        <v>0.53</v>
       </c>
       <c r="S364" t="n">
         <v>9.5</v>
@@ -19550,7 +19550,7 @@
         </is>
       </c>
       <c r="R365" t="n">
-        <v>-0.49</v>
+        <v>0.9</v>
       </c>
       <c r="S365" t="n">
         <v>9</v>
@@ -19601,7 +19601,7 @@
         </is>
       </c>
       <c r="R366" t="n">
-        <v>-0.48</v>
+        <v>0.93</v>
       </c>
       <c r="S366" t="n">
         <v>7</v>
@@ -19656,7 +19656,7 @@
         </is>
       </c>
       <c r="R367" t="n">
-        <v>-0.49</v>
+        <v>0.95</v>
       </c>
       <c r="S367" t="n">
         <v>8.5</v>
@@ -19707,7 +19707,7 @@
         </is>
       </c>
       <c r="R368" t="n">
-        <v>-0.5</v>
+        <v>0.55</v>
       </c>
       <c r="S368" t="n">
         <v>7.5</v>
@@ -19758,7 +19758,7 @@
         </is>
       </c>
       <c r="R369" t="n">
-        <v>-0.49</v>
+        <v>0.13</v>
       </c>
       <c r="S369" t="n">
         <v>5</v>
@@ -19809,7 +19809,7 @@
         </is>
       </c>
       <c r="R370" t="n">
-        <v>-0.49</v>
+        <v>0.8</v>
       </c>
       <c r="S370" t="n">
         <v>7</v>
@@ -19860,7 +19860,7 @@
         </is>
       </c>
       <c r="R371" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="S371" t="n">
         <v>7.5</v>
@@ -19911,7 +19911,7 @@
         </is>
       </c>
       <c r="R372" t="n">
-        <v>-0.49</v>
+        <v>0.51</v>
       </c>
       <c r="S372" t="n">
         <v>7.5</v>
@@ -19962,7 +19962,7 @@
         </is>
       </c>
       <c r="R373" t="n">
-        <v>-0.48</v>
+        <v>0.95</v>
       </c>
       <c r="S373" t="n">
         <v>7.5</v>
@@ -20015,7 +20015,7 @@
         </is>
       </c>
       <c r="R374" t="n">
-        <v>-0.48</v>
+        <v>0.96</v>
       </c>
       <c r="S374" t="n">
         <v>8.5</v>
@@ -20066,7 +20066,7 @@
         </is>
       </c>
       <c r="R375" t="n">
-        <v>-0.5</v>
+        <v>0.55</v>
       </c>
       <c r="S375" t="n">
         <v>7.5</v>
@@ -20119,7 +20119,7 @@
         </is>
       </c>
       <c r="R376" t="n">
-        <v>-0.51</v>
+        <v>0.83</v>
       </c>
       <c r="S376" t="n">
         <v>7.5</v>
@@ -20172,7 +20172,7 @@
         </is>
       </c>
       <c r="R377" t="n">
-        <v>-0.49</v>
+        <v>0.96</v>
       </c>
       <c r="S377" t="n">
         <v>7</v>
@@ -20223,7 +20223,7 @@
         </is>
       </c>
       <c r="R378" t="n">
-        <v>-0.48</v>
+        <v>0.67</v>
       </c>
       <c r="S378" t="n">
         <v>8.5</v>
@@ -20274,7 +20274,7 @@
         </is>
       </c>
       <c r="R379" t="n">
-        <v>-0.49</v>
+        <v>0.97</v>
       </c>
       <c r="S379" t="n">
         <v>8.5</v>
@@ -20325,7 +20325,7 @@
         </is>
       </c>
       <c r="R380" t="n">
-        <v>-0.51</v>
+        <v>-0.44</v>
       </c>
       <c r="S380" t="n">
         <v>5</v>
@@ -20380,7 +20380,7 @@
         </is>
       </c>
       <c r="R381" t="n">
-        <v>-0.5</v>
+        <v>0.54</v>
       </c>
       <c r="S381" t="n">
         <v>7</v>
@@ -20431,7 +20431,7 @@
         </is>
       </c>
       <c r="R382" t="n">
-        <v>-0.48</v>
+        <v>0.5</v>
       </c>
       <c r="S382" t="n">
         <v>7</v>
@@ -20482,7 +20482,7 @@
         </is>
       </c>
       <c r="R383" t="n">
-        <v>-0.48</v>
+        <v>0.67</v>
       </c>
       <c r="S383" t="n">
         <v>8.5</v>
@@ -20533,7 +20533,7 @@
         </is>
       </c>
       <c r="R384" t="n">
-        <v>-0.5</v>
+        <v>0.55</v>
       </c>
       <c r="S384" t="n">
         <v>7.5</v>
@@ -20586,7 +20586,7 @@
         </is>
       </c>
       <c r="R385" t="n">
-        <v>-0.49</v>
+        <v>0.92</v>
       </c>
       <c r="S385" t="n">
         <v>8.5</v>
@@ -20639,7 +20639,7 @@
         </is>
       </c>
       <c r="R386" t="n">
-        <v>-0.5</v>
+        <v>0.72</v>
       </c>
       <c r="S386" t="n">
         <v>7.5</v>
@@ -20690,7 +20690,7 @@
         </is>
       </c>
       <c r="R387" t="n">
-        <v>-0.49</v>
+        <v>0.51</v>
       </c>
       <c r="S387" t="n">
         <v>7.5</v>
@@ -20741,7 +20741,7 @@
         </is>
       </c>
       <c r="R388" t="n">
-        <v>-0.49</v>
+        <v>0.59</v>
       </c>
       <c r="S388" t="n">
         <v>8.5</v>
@@ -20796,7 +20796,7 @@
         </is>
       </c>
       <c r="R389" t="n">
-        <v>-0.5</v>
+        <v>-0.02</v>
       </c>
       <c r="S389" t="n">
         <v>7</v>
@@ -20847,7 +20847,7 @@
         </is>
       </c>
       <c r="R390" t="n">
-        <v>-0.5</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S390" t="n">
         <v>7.5</v>
@@ -20898,7 +20898,7 @@
         </is>
       </c>
       <c r="R391" t="n">
-        <v>-0.49</v>
+        <v>0.13</v>
       </c>
       <c r="S391" t="n">
         <v>5</v>
@@ -20949,7 +20949,7 @@
         </is>
       </c>
       <c r="R392" t="n">
-        <v>-0.5</v>
+        <v>0.55</v>
       </c>
       <c r="S392" t="n">
         <v>7.5</v>
@@ -21002,7 +21002,7 @@
         </is>
       </c>
       <c r="R393" t="n">
-        <v>-0.49</v>
+        <v>0.79</v>
       </c>
       <c r="S393" t="n">
         <v>7.5</v>
@@ -21053,7 +21053,7 @@
         </is>
       </c>
       <c r="R394" t="n">
-        <v>-0.49</v>
+        <v>0.96</v>
       </c>
       <c r="S394" t="n">
         <v>7.5</v>
@@ -21104,7 +21104,7 @@
         </is>
       </c>
       <c r="R395" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="S395" t="n">
         <v>7.5</v>
@@ -21161,7 +21161,7 @@
         </is>
       </c>
       <c r="R396" t="n">
-        <v>-0.48</v>
+        <v>0.97</v>
       </c>
       <c r="S396" t="n">
         <v>8.5</v>
@@ -21212,7 +21212,7 @@
         </is>
       </c>
       <c r="R397" t="n">
-        <v>-0.48</v>
+        <v>0.39</v>
       </c>
       <c r="S397" t="n">
         <v>7</v>
@@ -21267,7 +21267,7 @@
         </is>
       </c>
       <c r="R398" t="n">
-        <v>-0.48</v>
+        <v>0.79</v>
       </c>
       <c r="S398" t="n">
         <v>8</v>
@@ -21318,7 +21318,7 @@
         </is>
       </c>
       <c r="R399" t="n">
-        <v>-0.5</v>
+        <v>0.55</v>
       </c>
       <c r="S399" t="n">
         <v>7.5</v>
@@ -21369,7 +21369,7 @@
         </is>
       </c>
       <c r="R400" t="n">
-        <v>-0.49</v>
+        <v>0.51</v>
       </c>
       <c r="S400" t="n">
         <v>7.5</v>
@@ -21420,7 +21420,7 @@
         </is>
       </c>
       <c r="R401" t="n">
-        <v>-0.48</v>
+        <v>0.9</v>
       </c>
       <c r="S401" t="n">
         <v>7.5</v>
@@ -21471,7 +21471,7 @@
         </is>
       </c>
       <c r="R402" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="S402" t="n">
         <v>7.5</v>
@@ -21526,7 +21526,7 @@
         </is>
       </c>
       <c r="R403" t="n">
-        <v>-0.49</v>
+        <v>0.09</v>
       </c>
       <c r="S403" t="n">
         <v>6</v>
@@ -21579,7 +21579,7 @@
         </is>
       </c>
       <c r="R404" t="n">
-        <v>-0.49</v>
+        <v>0.91</v>
       </c>
       <c r="S404" t="n">
         <v>8</v>
@@ -21630,7 +21630,7 @@
         </is>
       </c>
       <c r="R405" t="n">
-        <v>-0.49</v>
+        <v>0.95</v>
       </c>
       <c r="S405" t="n">
         <v>7</v>
@@ -21681,7 +21681,7 @@
         </is>
       </c>
       <c r="R406" t="n">
-        <v>-0.5</v>
+        <v>0.55</v>
       </c>
       <c r="S406" t="n">
         <v>7.5</v>
@@ -21732,7 +21732,7 @@
         </is>
       </c>
       <c r="R407" t="n">
-        <v>-0.5</v>
+        <v>0.61</v>
       </c>
       <c r="S407" t="n">
         <v>7.5</v>
@@ -21783,7 +21783,7 @@
         </is>
       </c>
       <c r="R408" t="n">
-        <v>-0.49</v>
+        <v>-0.08</v>
       </c>
       <c r="S408" t="n">
         <v>5</v>
@@ -21834,7 +21834,7 @@
         </is>
       </c>
       <c r="R409" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="S409" t="n">
         <v>7.5</v>
@@ -21885,7 +21885,7 @@
         </is>
       </c>
       <c r="R410" t="n">
-        <v>-0.49</v>
+        <v>0.92</v>
       </c>
       <c r="S410" t="n">
         <v>9</v>
@@ -21940,7 +21940,7 @@
         </is>
       </c>
       <c r="R411" t="n">
-        <v>-0.5</v>
+        <v>0.65</v>
       </c>
       <c r="S411" t="n">
         <v>7</v>
@@ -21991,7 +21991,7 @@
         </is>
       </c>
       <c r="R412" t="n">
-        <v>-0.49</v>
+        <v>0.9</v>
       </c>
       <c r="S412" t="n">
         <v>8</v>
@@ -22042,7 +22042,7 @@
         </is>
       </c>
       <c r="R413" t="n">
-        <v>-0.5</v>
+        <v>0.97</v>
       </c>
       <c r="S413" t="n">
         <v>6.5</v>
@@ -22093,7 +22093,7 @@
         </is>
       </c>
       <c r="R414" t="n">
-        <v>-0.49</v>
+        <v>0.84</v>
       </c>
       <c r="S414" t="n">
         <v>7</v>
@@ -22144,7 +22144,7 @@
         </is>
       </c>
       <c r="R415" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="S415" t="n">
         <v>7.5</v>
@@ -22199,7 +22199,7 @@
         </is>
       </c>
       <c r="R416" t="n">
-        <v>-0.48</v>
+        <v>0.82</v>
       </c>
       <c r="S416" t="n">
         <v>7.5</v>
@@ -22250,7 +22250,7 @@
         </is>
       </c>
       <c r="R417" t="n">
-        <v>-0.5</v>
+        <v>0.55</v>
       </c>
       <c r="S417" t="n">
         <v>7.5</v>
@@ -22301,7 +22301,7 @@
         </is>
       </c>
       <c r="R418" t="n">
-        <v>-0.49</v>
+        <v>0.86</v>
       </c>
       <c r="S418" t="n">
         <v>8</v>
@@ -22352,7 +22352,7 @@
         </is>
       </c>
       <c r="R419" t="n">
-        <v>-0.5</v>
+        <v>0.97</v>
       </c>
       <c r="S419" t="n">
         <v>8</v>
@@ -22405,7 +22405,7 @@
         </is>
       </c>
       <c r="R420" t="n">
-        <v>-0.48</v>
+        <v>0.98</v>
       </c>
       <c r="S420" t="n">
         <v>8.5</v>
@@ -22456,7 +22456,7 @@
         </is>
       </c>
       <c r="R421" t="n">
-        <v>-0.48</v>
+        <v>0.87</v>
       </c>
       <c r="S421" t="n">
         <v>8.5</v>
@@ -22507,7 +22507,7 @@
         </is>
       </c>
       <c r="R422" t="n">
-        <v>-0.49</v>
+        <v>0.96</v>
       </c>
       <c r="S422" t="n">
         <v>8</v>
@@ -22558,7 +22558,7 @@
         </is>
       </c>
       <c r="R423" t="n">
-        <v>-0.49</v>
+        <v>0.8</v>
       </c>
       <c r="S423" t="n">
         <v>7</v>
@@ -22609,7 +22609,7 @@
         </is>
       </c>
       <c r="R424" t="n">
-        <v>-0.49</v>
+        <v>0.18</v>
       </c>
       <c r="S424" t="n">
         <v>9</v>
@@ -22660,7 +22660,7 @@
         </is>
       </c>
       <c r="R425" t="n">
-        <v>-0.49</v>
+        <v>0.98</v>
       </c>
       <c r="S425" t="n">
         <v>8</v>
@@ -22711,7 +22711,7 @@
         </is>
       </c>
       <c r="R426" t="n">
-        <v>-0.49</v>
+        <v>0.92</v>
       </c>
       <c r="S426" t="n">
         <v>9</v>
@@ -22764,7 +22764,7 @@
         </is>
       </c>
       <c r="R427" t="n">
-        <v>-0.49</v>
+        <v>0.97</v>
       </c>
       <c r="S427" t="n">
         <v>9.5</v>
@@ -22815,7 +22815,7 @@
         </is>
       </c>
       <c r="R428" t="n">
-        <v>-0.47</v>
+        <v>0.42</v>
       </c>
       <c r="S428" t="n">
         <v>8.5</v>
@@ -22866,7 +22866,7 @@
         </is>
       </c>
       <c r="R429" t="n">
-        <v>-0.49</v>
+        <v>0.13</v>
       </c>
       <c r="S429" t="n">
         <v>5</v>
@@ -22917,7 +22917,7 @@
         </is>
       </c>
       <c r="R430" t="n">
-        <v>-0.49</v>
+        <v>0.85</v>
       </c>
       <c r="S430" t="n">
         <v>7.5</v>
@@ -22970,7 +22970,7 @@
         </is>
       </c>
       <c r="R431" t="n">
-        <v>-0.47</v>
+        <v>0.92</v>
       </c>
       <c r="S431" t="n">
         <v>7.5</v>
@@ -23021,7 +23021,7 @@
         </is>
       </c>
       <c r="R432" t="n">
-        <v>-0.5</v>
+        <v>0.3</v>
       </c>
       <c r="S432" t="n">
         <v>6.5</v>
@@ -23072,7 +23072,7 @@
         </is>
       </c>
       <c r="R433" t="n">
-        <v>-0.49</v>
+        <v>0.9</v>
       </c>
       <c r="S433" t="n">
         <v>8.5</v>
@@ -23123,7 +23123,7 @@
         </is>
       </c>
       <c r="R434" t="n">
-        <v>-0.48</v>
+        <v>0.64</v>
       </c>
       <c r="S434" t="n">
         <v>9.5</v>
@@ -23174,7 +23174,7 @@
         </is>
       </c>
       <c r="R435" t="n">
-        <v>-0.5</v>
+        <v>0.97</v>
       </c>
       <c r="S435" t="n">
         <v>8</v>
@@ -23225,7 +23225,7 @@
         </is>
       </c>
       <c r="R436" t="n">
-        <v>-0.5</v>
+        <v>0.92</v>
       </c>
       <c r="S436" t="n">
         <v>9.5</v>
@@ -23276,7 +23276,7 @@
         </is>
       </c>
       <c r="R437" t="n">
-        <v>-0.5</v>
+        <v>0.88</v>
       </c>
       <c r="S437" t="n">
         <v>8.5</v>
@@ -23327,7 +23327,7 @@
         </is>
       </c>
       <c r="R438" t="n">
-        <v>-0.49</v>
+        <v>0.96</v>
       </c>
       <c r="S438" t="n">
         <v>8</v>
@@ -23378,7 +23378,7 @@
         </is>
       </c>
       <c r="R439" t="n">
-        <v>-0.49</v>
+        <v>0.97</v>
       </c>
       <c r="S439" t="n">
         <v>7.5</v>
@@ -23435,7 +23435,7 @@
         </is>
       </c>
       <c r="R440" t="n">
-        <v>-0.49</v>
+        <v>0.98</v>
       </c>
       <c r="S440" t="n">
         <v>8.5</v>
@@ -23488,7 +23488,7 @@
         </is>
       </c>
       <c r="R441" t="n">
-        <v>-0.47</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S441" t="n">
         <v>8.5</v>
@@ -23543,7 +23543,7 @@
         </is>
       </c>
       <c r="R442" t="n">
-        <v>-0.49</v>
+        <v>0.98</v>
       </c>
       <c r="S442" t="n">
         <v>8.5</v>
@@ -23596,7 +23596,7 @@
         </is>
       </c>
       <c r="R443" t="n">
-        <v>-0.47</v>
+        <v>0.89</v>
       </c>
       <c r="S443" t="n">
         <v>8.5</v>
@@ -23649,7 +23649,7 @@
         </is>
       </c>
       <c r="R444" t="n">
-        <v>-0.48</v>
+        <v>0.93</v>
       </c>
       <c r="S444" t="n">
         <v>8.5</v>
@@ -23700,7 +23700,7 @@
         </is>
       </c>
       <c r="R445" t="n">
-        <v>-0.48</v>
+        <v>0.98</v>
       </c>
       <c r="S445" t="n">
         <v>8</v>
@@ -23755,7 +23755,7 @@
         </is>
       </c>
       <c r="R446" t="n">
-        <v>-0.51</v>
+        <v>0.89</v>
       </c>
       <c r="S446" t="n">
         <v>8</v>
@@ -23806,7 +23806,7 @@
         </is>
       </c>
       <c r="R447" t="n">
-        <v>-0.49</v>
+        <v>0.95</v>
       </c>
       <c r="S447" t="n">
         <v>6.5</v>
@@ -23857,7 +23857,7 @@
         </is>
       </c>
       <c r="R448" t="n">
-        <v>-0.5</v>
+        <v>0.8</v>
       </c>
       <c r="S448" t="n">
         <v>9.5</v>
@@ -23910,7 +23910,7 @@
         </is>
       </c>
       <c r="R449" t="n">
-        <v>-0.5</v>
+        <v>0.86</v>
       </c>
       <c r="S449" t="n">
         <v>6</v>
@@ -23963,7 +23963,7 @@
         </is>
       </c>
       <c r="R450" t="n">
-        <v>-0.49</v>
+        <v>0.98</v>
       </c>
       <c r="S450" t="n">
         <v>8</v>
@@ -24018,7 +24018,7 @@
         </is>
       </c>
       <c r="R451" t="n">
-        <v>-0.51</v>
+        <v>0.79</v>
       </c>
       <c r="S451" t="n">
         <v>8</v>
@@ -24069,7 +24069,7 @@
         </is>
       </c>
       <c r="R452" t="n">
-        <v>-0.49</v>
+        <v>0.3</v>
       </c>
       <c r="S452" t="n">
         <v>7.5</v>
@@ -24120,7 +24120,7 @@
         </is>
       </c>
       <c r="R453" t="n">
-        <v>-0.48</v>
+        <v>-0.04</v>
       </c>
       <c r="S453" t="n">
         <v>7</v>
@@ -24171,7 +24171,7 @@
         </is>
       </c>
       <c r="R454" t="n">
-        <v>-0.5</v>
+        <v>0.19</v>
       </c>
       <c r="S454" t="n">
         <v>6</v>
@@ -24226,7 +24226,7 @@
         </is>
       </c>
       <c r="R455" t="n">
-        <v>-0.48</v>
+        <v>0.98</v>
       </c>
       <c r="S455" t="n">
         <v>7</v>
@@ -24277,7 +24277,7 @@
         </is>
       </c>
       <c r="R456" t="n">
-        <v>-0.48</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S456" t="n">
         <v>9</v>
@@ -24328,7 +24328,7 @@
         </is>
       </c>
       <c r="R457" t="n">
-        <v>-0.49</v>
+        <v>0.92</v>
       </c>
       <c r="S457" t="n">
         <v>8</v>
@@ -24379,7 +24379,7 @@
         </is>
       </c>
       <c r="R458" t="n">
-        <v>-0.49</v>
+        <v>0.93</v>
       </c>
       <c r="S458" t="n">
         <v>9.5</v>
@@ -24432,7 +24432,7 @@
         </is>
       </c>
       <c r="R459" t="n">
-        <v>-0.51</v>
+        <v>0.98</v>
       </c>
       <c r="S459" t="n">
         <v>8</v>
@@ -24483,7 +24483,7 @@
         </is>
       </c>
       <c r="R460" t="n">
-        <v>-0.48</v>
+        <v>0.95</v>
       </c>
       <c r="S460" t="n">
         <v>9.5</v>
@@ -24534,7 +24534,7 @@
         </is>
       </c>
       <c r="R461" t="n">
-        <v>-0.49</v>
+        <v>0.2</v>
       </c>
       <c r="S461" t="n">
         <v>7</v>
@@ -24589,7 +24589,7 @@
         </is>
       </c>
       <c r="R462" t="n">
-        <v>-0.49</v>
+        <v>0.78</v>
       </c>
       <c r="S462" t="n">
         <v>8.5</v>
@@ -24642,7 +24642,7 @@
         </is>
       </c>
       <c r="R463" t="n">
-        <v>-0.49</v>
+        <v>-0.4</v>
       </c>
       <c r="S463" t="n">
         <v>5.5</v>
@@ -24695,7 +24695,7 @@
         </is>
       </c>
       <c r="R464" t="n">
-        <v>-0.47</v>
+        <v>0.98</v>
       </c>
       <c r="S464" t="n">
         <v>8</v>
@@ -24746,7 +24746,7 @@
         </is>
       </c>
       <c r="R465" t="n">
-        <v>-0.5</v>
+        <v>0.92</v>
       </c>
       <c r="S465" t="n">
         <v>9.5</v>
@@ -24797,7 +24797,7 @@
         </is>
       </c>
       <c r="R466" t="n">
-        <v>-0.49</v>
+        <v>0.13</v>
       </c>
       <c r="S466" t="n">
         <v>5</v>
@@ -24850,7 +24850,7 @@
         </is>
       </c>
       <c r="R467" t="n">
-        <v>-0.49</v>
+        <v>0.98</v>
       </c>
       <c r="S467" t="n">
         <v>8.5</v>
@@ -24905,7 +24905,7 @@
         </is>
       </c>
       <c r="R468" t="n">
-        <v>-0.49</v>
+        <v>0.98</v>
       </c>
       <c r="S468" t="n">
         <v>8.5</v>
@@ -24956,7 +24956,7 @@
         </is>
       </c>
       <c r="R469" t="n">
-        <v>-0.5</v>
+        <v>0.55</v>
       </c>
       <c r="S469" t="n">
         <v>7.5</v>
@@ -25007,7 +25007,7 @@
         </is>
       </c>
       <c r="R470" t="n">
-        <v>-0.5</v>
+        <v>0.92</v>
       </c>
       <c r="S470" t="n">
         <v>9.5</v>
@@ -25058,7 +25058,7 @@
         </is>
       </c>
       <c r="R471" t="n">
-        <v>-0.48</v>
+        <v>0.39</v>
       </c>
       <c r="S471" t="n">
         <v>7</v>
@@ -25109,7 +25109,7 @@
         </is>
       </c>
       <c r="R472" t="n">
-        <v>-0.49</v>
+        <v>0.92</v>
       </c>
       <c r="S472" t="n">
         <v>9</v>
@@ -25162,7 +25162,7 @@
         </is>
       </c>
       <c r="R473" t="n">
-        <v>-0.5</v>
+        <v>0.86</v>
       </c>
       <c r="S473" t="n">
         <v>5.5</v>
@@ -25215,7 +25215,7 @@
         </is>
       </c>
       <c r="R474" t="n">
-        <v>-0.49</v>
+        <v>0.98</v>
       </c>
       <c r="S474" t="n">
         <v>8.5</v>
@@ -25268,7 +25268,7 @@
         </is>
       </c>
       <c r="R475" t="n">
-        <v>-0.49</v>
+        <v>0.88</v>
       </c>
       <c r="S475" t="n">
         <v>7.5</v>
@@ -25319,7 +25319,7 @@
         </is>
       </c>
       <c r="R476" t="n">
-        <v>-0.47</v>
+        <v>0.41</v>
       </c>
       <c r="S476" t="n">
         <v>6</v>
@@ -25376,7 +25376,7 @@
         </is>
       </c>
       <c r="R477" t="n">
-        <v>-0.5</v>
+        <v>0.97</v>
       </c>
       <c r="S477" t="n">
         <v>8.5</v>
@@ -25429,7 +25429,7 @@
         </is>
       </c>
       <c r="R478" t="n">
-        <v>-0.51</v>
+        <v>0.25</v>
       </c>
       <c r="S478" t="n">
         <v>6.5</v>
@@ -25480,7 +25480,7 @@
         </is>
       </c>
       <c r="R479" t="n">
-        <v>-0.47</v>
+        <v>0.96</v>
       </c>
       <c r="S479" t="n">
         <v>8</v>
@@ -25535,7 +25535,7 @@
         </is>
       </c>
       <c r="R480" t="n">
-        <v>-0.49</v>
+        <v>0.93</v>
       </c>
       <c r="S480" t="n">
         <v>6.5</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="R481" t="n">
-        <v>-0.49</v>
+        <v>0.63</v>
       </c>
       <c r="S481" t="n">
         <v>9.5</v>
@@ -25641,7 +25641,7 @@
         </is>
       </c>
       <c r="R482" t="n">
-        <v>-0.5</v>
+        <v>0.96</v>
       </c>
       <c r="S482" t="n">
         <v>7.5</v>
@@ -25692,7 +25692,7 @@
         </is>
       </c>
       <c r="R483" t="n">
-        <v>-0.49</v>
+        <v>0.96</v>
       </c>
       <c r="S483" t="n">
         <v>8</v>
@@ -25743,7 +25743,7 @@
         </is>
       </c>
       <c r="R484" t="n">
-        <v>-0.47</v>
+        <v>0.97</v>
       </c>
       <c r="S484" t="n">
         <v>8.5</v>
@@ -25794,7 +25794,7 @@
         </is>
       </c>
       <c r="R485" t="n">
-        <v>-0.49</v>
+        <v>0.88</v>
       </c>
       <c r="S485" t="n">
         <v>7.5</v>
@@ -25845,7 +25845,7 @@
         </is>
       </c>
       <c r="R486" t="n">
-        <v>-0.47</v>
+        <v>0.97</v>
       </c>
       <c r="S486" t="n">
         <v>8.5</v>
@@ -25898,7 +25898,7 @@
         </is>
       </c>
       <c r="R487" t="n">
-        <v>-0.5</v>
+        <v>0.98</v>
       </c>
       <c r="S487" t="n">
         <v>8.5</v>
@@ -25951,7 +25951,7 @@
         </is>
       </c>
       <c r="R488" t="n">
-        <v>-0.51</v>
+        <v>0.87</v>
       </c>
       <c r="S488" t="n">
         <v>8</v>
@@ -26002,7 +26002,7 @@
         </is>
       </c>
       <c r="R489" t="n">
-        <v>-0.5</v>
+        <v>0.85</v>
       </c>
       <c r="S489" t="n">
         <v>8</v>
@@ -26053,7 +26053,7 @@
         </is>
       </c>
       <c r="R490" t="n">
-        <v>-0.49</v>
+        <v>0.59</v>
       </c>
       <c r="S490" t="n">
         <v>7.5</v>
@@ -26108,7 +26108,7 @@
         </is>
       </c>
       <c r="R491" t="n">
-        <v>-0.49</v>
+        <v>0.78</v>
       </c>
       <c r="S491" t="n">
         <v>7.5</v>
@@ -26159,7 +26159,7 @@
         </is>
       </c>
       <c r="R492" t="n">
-        <v>-0.47</v>
+        <v>0.96</v>
       </c>
       <c r="S492" t="n">
         <v>9</v>
@@ -26212,7 +26212,7 @@
         </is>
       </c>
       <c r="R493" t="n">
-        <v>-0.51</v>
+        <v>0.18</v>
       </c>
       <c r="S493" t="n">
         <v>7</v>
@@ -26263,7 +26263,7 @@
         </is>
       </c>
       <c r="R494" t="n">
-        <v>-0.49</v>
+        <v>0.9</v>
       </c>
       <c r="S494" t="n">
         <v>9</v>
@@ -26314,7 +26314,7 @@
         </is>
       </c>
       <c r="R495" t="n">
-        <v>-0.5</v>
+        <v>0.97</v>
       </c>
       <c r="S495" t="n">
         <v>7.5</v>
@@ -26365,7 +26365,7 @@
         </is>
       </c>
       <c r="R496" t="n">
-        <v>-0.5</v>
+        <v>0.66</v>
       </c>
       <c r="S496" t="n">
         <v>7.5</v>
@@ -26416,7 +26416,7 @@
         </is>
       </c>
       <c r="R497" t="n">
-        <v>-0.5</v>
+        <v>0.91</v>
       </c>
       <c r="S497" t="n">
         <v>7.5</v>
@@ -26467,7 +26467,7 @@
         </is>
       </c>
       <c r="R498" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="S498" t="n">
         <v>8.5</v>
@@ -26518,7 +26518,7 @@
         </is>
       </c>
       <c r="R499" t="n">
-        <v>-0.49</v>
+        <v>0.8</v>
       </c>
       <c r="S499" t="n">
         <v>7</v>
@@ -26571,7 +26571,7 @@
         </is>
       </c>
       <c r="R500" t="n">
-        <v>-0.48</v>
+        <v>0.92</v>
       </c>
       <c r="S500" t="n">
         <v>8</v>
@@ -26622,7 +26622,7 @@
         </is>
       </c>
       <c r="R501" t="n">
-        <v>-0.5</v>
+        <v>0.9</v>
       </c>
       <c r="S501" t="n">
         <v>7</v>
@@ -26679,7 +26679,7 @@
         </is>
       </c>
       <c r="R502" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="S502" t="n">
         <v>7.5</v>
@@ -26730,7 +26730,7 @@
         </is>
       </c>
       <c r="R503" t="n">
-        <v>-0.5</v>
+        <v>0.97</v>
       </c>
       <c r="S503" t="n">
         <v>7.5</v>
@@ -26783,7 +26783,7 @@
         </is>
       </c>
       <c r="R504" t="n">
-        <v>-0.51</v>
+        <v>0.96</v>
       </c>
       <c r="S504" t="n">
         <v>8</v>
@@ -26838,7 +26838,7 @@
         </is>
       </c>
       <c r="R505" t="n">
-        <v>-0.5</v>
+        <v>0.99</v>
       </c>
       <c r="S505" t="n">
         <v>9</v>
@@ -26889,7 +26889,7 @@
         </is>
       </c>
       <c r="R506" t="n">
-        <v>-0.49</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S506" t="n">
         <v>8</v>
@@ -26942,7 +26942,7 @@
         </is>
       </c>
       <c r="R507" t="n">
-        <v>-0.49</v>
+        <v>0.28</v>
       </c>
       <c r="S507" t="n">
         <v>6</v>
@@ -26993,7 +26993,7 @@
         </is>
       </c>
       <c r="R508" t="n">
-        <v>-0.49</v>
+        <v>0.61</v>
       </c>
       <c r="S508" t="n">
         <v>5.5</v>
@@ -27046,7 +27046,7 @@
         </is>
       </c>
       <c r="R509" t="n">
-        <v>-0.48</v>
+        <v>0.88</v>
       </c>
       <c r="S509" t="n">
         <v>7.5</v>
@@ -27097,7 +27097,7 @@
         </is>
       </c>
       <c r="R510" t="n">
-        <v>-0.49</v>
+        <v>0.84</v>
       </c>
       <c r="S510" t="n">
         <v>5</v>
@@ -27148,7 +27148,7 @@
         </is>
       </c>
       <c r="R511" t="n">
-        <v>-0.49</v>
+        <v>-0.36</v>
       </c>
       <c r="S511" t="n">
         <v>6</v>
@@ -27199,7 +27199,7 @@
         </is>
       </c>
       <c r="R512" t="n">
-        <v>-0.49</v>
+        <v>0.93</v>
       </c>
       <c r="S512" t="n">
         <v>8</v>
@@ -27250,7 +27250,7 @@
         </is>
       </c>
       <c r="R513" t="n">
-        <v>-0.47</v>
+        <v>0.02</v>
       </c>
       <c r="S513" t="n">
         <v>7.5</v>
@@ -27301,7 +27301,7 @@
         </is>
       </c>
       <c r="R514" t="n">
-        <v>-0.49</v>
+        <v>0.9</v>
       </c>
       <c r="S514" t="n">
         <v>9</v>
@@ -27356,7 +27356,7 @@
         </is>
       </c>
       <c r="R515" t="n">
-        <v>-0.48</v>
+        <v>0.97</v>
       </c>
       <c r="S515" t="n">
         <v>9</v>
@@ -27407,7 +27407,7 @@
         </is>
       </c>
       <c r="R516" t="n">
-        <v>-0.5</v>
+        <v>0.97</v>
       </c>
       <c r="S516" t="n">
         <v>8</v>
@@ -27458,7 +27458,7 @@
         </is>
       </c>
       <c r="R517" t="n">
-        <v>-0.49</v>
+        <v>0.99</v>
       </c>
       <c r="S517" t="n">
         <v>9</v>
@@ -27509,7 +27509,7 @@
         </is>
       </c>
       <c r="R518" t="n">
-        <v>-0.5</v>
+        <v>0.92</v>
       </c>
       <c r="S518" t="n">
         <v>9.5</v>
@@ -27560,7 +27560,7 @@
         </is>
       </c>
       <c r="R519" t="n">
-        <v>-0.5</v>
+        <v>0.83</v>
       </c>
       <c r="S519" t="n">
         <v>7.5</v>
@@ -27611,7 +27611,7 @@
         </is>
       </c>
       <c r="R520" t="n">
-        <v>-0.48</v>
+        <v>0.93</v>
       </c>
       <c r="S520" t="n">
         <v>7</v>
@@ -27668,7 +27668,7 @@
         </is>
       </c>
       <c r="R521" t="n">
-        <v>-0.49</v>
+        <v>0.99</v>
       </c>
       <c r="S521" t="n">
         <v>8.5</v>
@@ -27725,7 +27725,7 @@
         </is>
       </c>
       <c r="R522" t="n">
-        <v>-0.49</v>
+        <v>0.97</v>
       </c>
       <c r="S522" t="n">
         <v>9.5</v>
@@ -27776,7 +27776,7 @@
         </is>
       </c>
       <c r="R523" t="n">
-        <v>-0.49</v>
+        <v>0.98</v>
       </c>
       <c r="S523" t="n">
         <v>8.5</v>
@@ -27827,7 +27827,7 @@
         </is>
       </c>
       <c r="R524" t="n">
-        <v>-0.49</v>
+        <v>0.18</v>
       </c>
       <c r="S524" t="n">
         <v>9</v>
@@ -27878,7 +27878,7 @@
         </is>
       </c>
       <c r="R525" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="S525" t="n">
         <v>7.5</v>
@@ -27929,7 +27929,7 @@
         </is>
       </c>
       <c r="R526" t="n">
-        <v>-0.5</v>
+        <v>0.55</v>
       </c>
       <c r="S526" t="n">
         <v>7.5</v>
@@ -27982,7 +27982,7 @@
         </is>
       </c>
       <c r="R527" t="n">
-        <v>-0.5</v>
+        <v>0.72</v>
       </c>
       <c r="S527" t="n">
         <v>7.5</v>
@@ -28035,7 +28035,7 @@
         </is>
       </c>
       <c r="R528" t="n">
-        <v>-0.48</v>
+        <v>0.98</v>
       </c>
       <c r="S528" t="n">
         <v>9.5</v>
@@ -28088,7 +28088,7 @@
         </is>
       </c>
       <c r="R529" t="n">
-        <v>-0.49</v>
+        <v>0.92</v>
       </c>
       <c r="S529" t="n">
         <v>5.5</v>
@@ -28139,7 +28139,7 @@
         </is>
       </c>
       <c r="R530" t="n">
-        <v>-0.48</v>
+        <v>0.67</v>
       </c>
       <c r="S530" t="n">
         <v>8.5</v>
@@ -28194,7 +28194,7 @@
         </is>
       </c>
       <c r="R531" t="n">
-        <v>-0.5</v>
+        <v>0.96</v>
       </c>
       <c r="S531" t="n">
         <v>7.5</v>
@@ -28249,7 +28249,7 @@
         </is>
       </c>
       <c r="R532" t="n">
-        <v>-0.49</v>
+        <v>0.98</v>
       </c>
       <c r="S532" t="n">
         <v>8</v>
@@ -28300,7 +28300,7 @@
         </is>
       </c>
       <c r="R533" t="n">
-        <v>-0.49</v>
+        <v>0.42</v>
       </c>
       <c r="S533" t="n">
         <v>6.5</v>
@@ -28351,7 +28351,7 @@
         </is>
       </c>
       <c r="R534" t="n">
-        <v>-0.5</v>
+        <v>0.55</v>
       </c>
       <c r="S534" t="n">
         <v>7.5</v>
@@ -28402,7 +28402,7 @@
         </is>
       </c>
       <c r="R535" t="n">
-        <v>-0.49</v>
+        <v>0.13</v>
       </c>
       <c r="S535" t="n">
         <v>5</v>
@@ -28453,7 +28453,7 @@
         </is>
       </c>
       <c r="R536" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="S536" t="n">
         <v>7.5</v>
@@ -28504,7 +28504,7 @@
         </is>
       </c>
       <c r="R537" t="n">
-        <v>-0.49</v>
+        <v>0.13</v>
       </c>
       <c r="S537" t="n">
         <v>5</v>
@@ -28555,7 +28555,7 @@
         </is>
       </c>
       <c r="R538" t="n">
-        <v>-0.49</v>
+        <v>0.18</v>
       </c>
       <c r="S538" t="n">
         <v>9</v>
@@ -28606,7 +28606,7 @@
         </is>
       </c>
       <c r="R539" t="n">
-        <v>-0.5</v>
+        <v>0.91</v>
       </c>
       <c r="S539" t="n">
         <v>8.5</v>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="R540" t="n">
-        <v>-0.49</v>
+        <v>0.63</v>
       </c>
       <c r="S540" t="n">
         <v>9.5</v>
@@ -28710,7 +28710,7 @@
         </is>
       </c>
       <c r="R541" t="n">
-        <v>-0.48</v>
+        <v>0.84</v>
       </c>
       <c r="S541" t="n">
         <v>8.5</v>
@@ -28763,7 +28763,7 @@
         </is>
       </c>
       <c r="R542" t="n">
-        <v>-0.49</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S542" t="n">
         <v>8</v>
@@ -28816,7 +28816,7 @@
         </is>
       </c>
       <c r="R543" t="n">
-        <v>-0.49</v>
+        <v>0.98</v>
       </c>
       <c r="S543" t="n">
         <v>9</v>
@@ -28867,7 +28867,7 @@
         </is>
       </c>
       <c r="R544" t="n">
-        <v>-0.49</v>
+        <v>0.13</v>
       </c>
       <c r="S544" t="n">
         <v>5</v>
@@ -28918,7 +28918,7 @@
         </is>
       </c>
       <c r="R545" t="n">
-        <v>-0.48</v>
+        <v>0.09</v>
       </c>
       <c r="S545" t="n">
         <v>6.5</v>
@@ -28969,7 +28969,7 @@
         </is>
       </c>
       <c r="R546" t="n">
-        <v>-0.49</v>
+        <v>0.18</v>
       </c>
       <c r="S546" t="n">
         <v>9</v>
@@ -29020,7 +29020,7 @@
         </is>
       </c>
       <c r="R547" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="S547" t="n">
         <v>7.5</v>
@@ -29071,7 +29071,7 @@
         </is>
       </c>
       <c r="R548" t="n">
-        <v>-0.5</v>
+        <v>0.97</v>
       </c>
       <c r="S548" t="n">
         <v>7.5</v>
@@ -29122,7 +29122,7 @@
         </is>
       </c>
       <c r="R549" t="n">
-        <v>-0.49</v>
+        <v>0.63</v>
       </c>
       <c r="S549" t="n">
         <v>9.5</v>
@@ -29173,7 +29173,7 @@
         </is>
       </c>
       <c r="R550" t="n">
-        <v>-0.5</v>
+        <v>0.66</v>
       </c>
       <c r="S550" t="n">
         <v>7.5</v>
@@ -29224,7 +29224,7 @@
         </is>
       </c>
       <c r="R551" t="n">
-        <v>-0.49</v>
+        <v>0.13</v>
       </c>
       <c r="S551" t="n">
         <v>5</v>
@@ -29275,7 +29275,7 @@
         </is>
       </c>
       <c r="R552" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="S552" t="n">
         <v>7.5</v>
@@ -29326,7 +29326,7 @@
         </is>
       </c>
       <c r="R553" t="n">
-        <v>-0.49</v>
+        <v>0.85</v>
       </c>
       <c r="S553" t="n">
         <v>7.5</v>
@@ -29377,7 +29377,7 @@
         </is>
       </c>
       <c r="R554" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="S554" t="n">
         <v>7.5</v>
@@ -29428,7 +29428,7 @@
         </is>
       </c>
       <c r="R555" t="n">
-        <v>-0.49</v>
+        <v>0.13</v>
       </c>
       <c r="S555" t="n">
         <v>5</v>
@@ -29479,7 +29479,7 @@
         </is>
       </c>
       <c r="R556" t="n">
-        <v>-0.48</v>
+        <v>0.9</v>
       </c>
       <c r="S556" t="n">
         <v>9</v>
@@ -29532,7 +29532,7 @@
         </is>
       </c>
       <c r="R557" t="n">
-        <v>-0.5</v>
+        <v>0.97</v>
       </c>
       <c r="S557" t="n">
         <v>7.5</v>
@@ -29585,7 +29585,7 @@
         </is>
       </c>
       <c r="R558" t="n">
-        <v>-0.5</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S558" t="n">
         <v>9</v>
@@ -29638,7 +29638,7 @@
         </is>
       </c>
       <c r="R559" t="n">
-        <v>-0.48</v>
+        <v>0.97</v>
       </c>
       <c r="S559" t="n">
         <v>8.5</v>
@@ -29689,7 +29689,7 @@
         </is>
       </c>
       <c r="R560" t="n">
-        <v>-0.48</v>
+        <v>0.97</v>
       </c>
       <c r="S560" t="n">
         <v>8</v>
@@ -29740,7 +29740,7 @@
         </is>
       </c>
       <c r="R561" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="S561" t="n">
         <v>7.5</v>
@@ -29791,7 +29791,7 @@
         </is>
       </c>
       <c r="R562" t="n">
-        <v>-0.49</v>
+        <v>0.18</v>
       </c>
       <c r="S562" t="n">
         <v>9</v>
@@ -29844,7 +29844,7 @@
         </is>
       </c>
       <c r="R563" t="n">
-        <v>-0.49</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S563" t="n">
         <v>8</v>
@@ -29895,7 +29895,7 @@
         </is>
       </c>
       <c r="R564" t="n">
-        <v>-0.5</v>
+        <v>0.91</v>
       </c>
       <c r="S564" t="n">
         <v>8.5</v>
@@ -29950,7 +29950,7 @@
         </is>
       </c>
       <c r="R565" t="n">
-        <v>-0.49</v>
+        <v>0.97</v>
       </c>
       <c r="S565" t="n">
         <v>8</v>
@@ -30001,7 +30001,7 @@
         </is>
       </c>
       <c r="R566" t="n">
-        <v>-0.48</v>
+        <v>0.93</v>
       </c>
       <c r="S566" t="n">
         <v>8</v>
@@ -30052,7 +30052,7 @@
         </is>
       </c>
       <c r="R567" t="n">
-        <v>-0.51</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="S567" t="n">
         <v>7</v>
@@ -30107,7 +30107,7 @@
         </is>
       </c>
       <c r="R568" t="n">
-        <v>-0.48</v>
+        <v>0.76</v>
       </c>
       <c r="S568" t="n">
         <v>7.5</v>
@@ -30160,7 +30160,7 @@
         </is>
       </c>
       <c r="R569" t="n">
-        <v>-0.47</v>
+        <v>0.98</v>
       </c>
       <c r="S569" t="n">
         <v>9.5</v>
@@ -30213,7 +30213,7 @@
         </is>
       </c>
       <c r="R570" t="n">
-        <v>-0.49</v>
+        <v>0.61</v>
       </c>
       <c r="S570" t="n">
         <v>7.5</v>
@@ -30268,7 +30268,7 @@
         </is>
       </c>
       <c r="R571" t="n">
-        <v>-0.49</v>
+        <v>0.95</v>
       </c>
       <c r="S571" t="n">
         <v>8</v>
@@ -30319,7 +30319,7 @@
         </is>
       </c>
       <c r="R572" t="n">
-        <v>-0.5</v>
+        <v>0.78</v>
       </c>
       <c r="S572" t="n">
         <v>8</v>
@@ -30372,7 +30372,7 @@
         </is>
       </c>
       <c r="R573" t="n">
-        <v>-0.51</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S573" t="n">
         <v>7.5</v>
@@ -30425,7 +30425,7 @@
         </is>
       </c>
       <c r="R574" t="n">
-        <v>-0.49</v>
+        <v>0.9</v>
       </c>
       <c r="S574" t="n">
         <v>8</v>
@@ -30478,7 +30478,7 @@
         </is>
       </c>
       <c r="R575" t="n">
-        <v>-0.47</v>
+        <v>0.97</v>
       </c>
       <c r="S575" t="n">
         <v>8.5</v>
@@ -30529,7 +30529,7 @@
         </is>
       </c>
       <c r="R576" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="S576" t="n">
         <v>7.5</v>
@@ -30582,7 +30582,7 @@
         </is>
       </c>
       <c r="R577" t="n">
-        <v>-0.48</v>
+        <v>0.83</v>
       </c>
       <c r="S577" t="n">
         <v>8.5</v>
@@ -30635,7 +30635,7 @@
         </is>
       </c>
       <c r="R578" t="n">
-        <v>-0.49</v>
+        <v>0.98</v>
       </c>
       <c r="S578" t="n">
         <v>8</v>
@@ -30686,7 +30686,7 @@
         </is>
       </c>
       <c r="R579" t="n">
-        <v>-0.49</v>
+        <v>0.18</v>
       </c>
       <c r="S579" t="n">
         <v>9</v>
@@ -30737,7 +30737,7 @@
         </is>
       </c>
       <c r="R580" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="S580" t="n">
         <v>7.5</v>
@@ -30788,7 +30788,7 @@
         </is>
       </c>
       <c r="R581" t="n">
-        <v>-0.48</v>
+        <v>0.64</v>
       </c>
       <c r="S581" t="n">
         <v>9.5</v>
@@ -30841,7 +30841,7 @@
         </is>
       </c>
       <c r="R582" t="n">
-        <v>-0.49</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S582" t="n">
         <v>8</v>
@@ -30892,7 +30892,7 @@
         </is>
       </c>
       <c r="R583" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="S583" t="n">
         <v>7.5</v>
@@ -30943,7 +30943,7 @@
         </is>
       </c>
       <c r="R584" t="n">
-        <v>-0.49</v>
+        <v>0.18</v>
       </c>
       <c r="S584" t="n">
         <v>9</v>
@@ -30994,7 +30994,7 @@
         </is>
       </c>
       <c r="R585" t="n">
-        <v>-0.5</v>
+        <v>0.48</v>
       </c>
       <c r="S585" t="n">
         <v>8</v>
@@ -31045,7 +31045,7 @@
         </is>
       </c>
       <c r="R586" t="n">
-        <v>-0.49</v>
+        <v>0.13</v>
       </c>
       <c r="S586" t="n">
         <v>5</v>
@@ -31096,7 +31096,7 @@
         </is>
       </c>
       <c r="R587" t="n">
-        <v>-0.49</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="S587" t="n">
         <v>6</v>
@@ -31147,7 +31147,7 @@
         </is>
       </c>
       <c r="R588" t="n">
-        <v>-0.48</v>
+        <v>0.67</v>
       </c>
       <c r="S588" t="n">
         <v>8.5</v>
@@ -31198,7 +31198,7 @@
         </is>
       </c>
       <c r="R589" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="S589" t="n">
         <v>7.5</v>
@@ -31251,7 +31251,7 @@
         </is>
       </c>
       <c r="R590" t="n">
-        <v>-0.5</v>
+        <v>0.72</v>
       </c>
       <c r="S590" t="n">
         <v>7.5</v>
@@ -31304,7 +31304,7 @@
         </is>
       </c>
       <c r="R591" t="n">
-        <v>-0.5</v>
+        <v>0.21</v>
       </c>
       <c r="S591" t="n">
         <v>6.5</v>
@@ -31355,7 +31355,7 @@
         </is>
       </c>
       <c r="R592" t="n">
-        <v>-0.48</v>
+        <v>0.12</v>
       </c>
       <c r="S592" t="n">
         <v>5</v>
@@ -31406,7 +31406,7 @@
         </is>
       </c>
       <c r="R593" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="S593" t="n">
         <v>7.5</v>
@@ -31457,7 +31457,7 @@
         </is>
       </c>
       <c r="R594" t="n">
-        <v>-0.49</v>
+        <v>0.18</v>
       </c>
       <c r="S594" t="n">
         <v>9</v>
@@ -31510,7 +31510,7 @@
         </is>
       </c>
       <c r="R595" t="n">
-        <v>-0.47</v>
+        <v>0.9</v>
       </c>
       <c r="S595" t="n">
         <v>8.5</v>
@@ -31563,7 +31563,7 @@
         </is>
       </c>
       <c r="R596" t="n">
-        <v>-0.48</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S596" t="n">
         <v>5</v>
@@ -31616,7 +31616,7 @@
         </is>
       </c>
       <c r="R597" t="n">
-        <v>-0.5</v>
+        <v>0.91</v>
       </c>
       <c r="S597" t="n">
         <v>7.5</v>
@@ -31669,7 +31669,7 @@
         </is>
       </c>
       <c r="R598" t="n">
-        <v>-0.51</v>
+        <v>0.74</v>
       </c>
       <c r="S598" t="n">
         <v>8</v>
@@ -31724,7 +31724,7 @@
         </is>
       </c>
       <c r="R599" t="n">
-        <v>-0.5</v>
+        <v>0.96</v>
       </c>
       <c r="S599" t="n">
         <v>8</v>
@@ -31775,7 +31775,7 @@
         </is>
       </c>
       <c r="R600" t="n">
-        <v>-0.51</v>
+        <v>0.91</v>
       </c>
       <c r="S600" t="n">
         <v>8.5</v>
@@ -31830,7 +31830,7 @@
         </is>
       </c>
       <c r="R601" t="n">
-        <v>-0.49</v>
+        <v>0.98</v>
       </c>
       <c r="S601" t="n">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         </is>
       </c>
       <c r="R602" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="S602" t="n">
         <v>7.5</v>
@@ -31934,7 +31934,7 @@
         </is>
       </c>
       <c r="R603" t="n">
-        <v>-0.5</v>
+        <v>0.77</v>
       </c>
       <c r="S603" t="n">
         <v>8.5</v>
@@ -31987,7 +31987,7 @@
         </is>
       </c>
       <c r="R604" t="n">
-        <v>-0.51</v>
+        <v>0.87</v>
       </c>
       <c r="S604" t="n">
         <v>7.5</v>
@@ -32038,7 +32038,7 @@
         </is>
       </c>
       <c r="R605" t="n">
-        <v>-0.5</v>
+        <v>0.95</v>
       </c>
       <c r="S605" t="n">
         <v>7.5</v>
@@ -32089,7 +32089,7 @@
         </is>
       </c>
       <c r="R606" t="n">
-        <v>-0.49</v>
+        <v>0.63</v>
       </c>
       <c r="S606" t="n">
         <v>9.5</v>
@@ -32140,7 +32140,7 @@
         </is>
       </c>
       <c r="R607" t="n">
-        <v>-0.5</v>
+        <v>0.55</v>
       </c>
       <c r="S607" t="n">
         <v>7.5</v>
@@ -32191,7 +32191,7 @@
         </is>
       </c>
       <c r="R608" t="n">
-        <v>-0.49</v>
+        <v>0.68</v>
       </c>
       <c r="S608" t="n">
         <v>7</v>
@@ -32242,7 +32242,7 @@
         </is>
       </c>
       <c r="R609" t="n">
-        <v>-0.49</v>
+        <v>0.13</v>
       </c>
       <c r="S609" t="n">
         <v>5</v>
@@ -32293,7 +32293,7 @@
         </is>
       </c>
       <c r="R610" t="n">
-        <v>-0.48</v>
+        <v>0.96</v>
       </c>
       <c r="S610" t="n">
         <v>8.5</v>
@@ -32346,7 +32346,7 @@
         </is>
       </c>
       <c r="R611" t="n">
-        <v>-0.49</v>
+        <v>0.98</v>
       </c>
       <c r="S611" t="n">
         <v>8</v>
@@ -32399,7 +32399,7 @@
         </is>
       </c>
       <c r="R612" t="n">
-        <v>-0.5</v>
+        <v>0.78</v>
       </c>
       <c r="S612" t="n">
         <v>7.5</v>
@@ -32450,7 +32450,7 @@
         </is>
       </c>
       <c r="R613" t="n">
-        <v>-0.49</v>
+        <v>0.18</v>
       </c>
       <c r="S613" t="n">
         <v>9</v>
@@ -32501,7 +32501,7 @@
         </is>
       </c>
       <c r="R614" t="n">
-        <v>-0.5</v>
+        <v>0.55</v>
       </c>
       <c r="S614" t="n">
         <v>7.5</v>
@@ -32552,7 +32552,7 @@
         </is>
       </c>
       <c r="R615" t="n">
-        <v>-0.49</v>
+        <v>0.95</v>
       </c>
       <c r="S615" t="n">
         <v>7</v>
@@ -32603,7 +32603,7 @@
         </is>
       </c>
       <c r="R616" t="n">
-        <v>-0.5</v>
+        <v>0.55</v>
       </c>
       <c r="S616" t="n">
         <v>7.5</v>
@@ -32654,7 +32654,7 @@
         </is>
       </c>
       <c r="R617" t="n">
-        <v>-0.49</v>
+        <v>0.59</v>
       </c>
       <c r="S617" t="n">
         <v>8.5</v>
@@ -32705,7 +32705,7 @@
         </is>
       </c>
       <c r="R618" t="n">
-        <v>-0.49</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S618" t="n">
         <v>9</v>
@@ -32760,7 +32760,7 @@
         </is>
       </c>
       <c r="R619" t="n">
-        <v>-0.48</v>
+        <v>0.97</v>
       </c>
       <c r="S619" t="n">
         <v>9</v>
@@ -32817,7 +32817,7 @@
         </is>
       </c>
       <c r="R620" t="n">
-        <v>-0.51</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S620" t="n">
         <v>8</v>
@@ -32868,7 +32868,7 @@
         </is>
       </c>
       <c r="R621" t="n">
-        <v>-0.47</v>
+        <v>0.92</v>
       </c>
       <c r="S621" t="n">
         <v>7.5</v>
@@ -32919,7 +32919,7 @@
         </is>
       </c>
       <c r="R622" t="n">
-        <v>-0.48</v>
+        <v>0.67</v>
       </c>
       <c r="S622" t="n">
         <v>8.5</v>
@@ -32974,7 +32974,7 @@
         </is>
       </c>
       <c r="R623" t="n">
-        <v>-0.49</v>
+        <v>0.88</v>
       </c>
       <c r="S623" t="n">
         <v>7.5</v>
@@ -33031,7 +33031,7 @@
         </is>
       </c>
       <c r="R624" t="n">
-        <v>-0.49</v>
+        <v>0.98</v>
       </c>
       <c r="S624" t="n">
         <v>9</v>
